--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.205315</v>
+        <v>-0.207818</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.203492</v>
+        <v>-0.205267</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>2</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.200207</v>
+        <v>-0.2018</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>3</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.194478</v>
+        <v>-0.19584</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>4</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.188628</v>
+        <v>-0.1928</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>5</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.175911</v>
+        <v>-0.178227</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>6</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.158008</v>
+        <v>-0.160127</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>7</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.136582</v>
+        <v>-0.137901</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>8</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.131558</v>
+        <v>-0.13188</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>9</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.11246</v>
+        <v>-0.113793</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>10</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.110894</v>
+        <v>-0.112496</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>11</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.109943</v>
+        <v>-0.110539</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>12</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.109883</v>
+        <v>-0.110379</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>13</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.10843</v>
+        <v>-0.108667</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>14</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.102392</v>
+        <v>-0.103606</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>15</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.101019</v>
+        <v>-0.101948</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>16</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.100689</v>
+        <v>-0.101404</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>17</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.096123</v>
+        <v>-0.09654500000000001</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>18</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.09611500000000001</v>
+        <v>-0.096209</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>19</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.095193</v>
+        <v>-0.095568</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>20</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.092874</v>
+        <v>-0.093581</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>21</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.09099699999999999</v>
+        <v>-0.091543</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>22</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.090748</v>
+        <v>-0.091071</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>23</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.089186</v>
+        <v>-0.090837</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>24</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.089084</v>
+        <v>-0.090379</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>25</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.088833</v>
+        <v>-0.089687</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>26</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.08845699999999999</v>
+        <v>-0.089355</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>27</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.088325</v>
+        <v>-0.08905299999999999</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>28</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.088278</v>
+        <v>-0.088712</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>29</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.088103</v>
+        <v>-0.088494</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>30</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.0881</v>
+        <v>-0.088453</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>31</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.086879</v>
+        <v>-0.087593</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>32</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.086642</v>
+        <v>-0.086775</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>33</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.08582099999999999</v>
+        <v>-0.086006</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>34</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.08550099999999999</v>
+        <v>-0.085965</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>35</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.08446099999999999</v>
+        <v>-0.08554100000000001</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>36</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.08434</v>
+        <v>-0.085217</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>37</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.082291</v>
+        <v>-0.083106</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>38</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.08215799999999999</v>
+        <v>-0.082623</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>39</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.081931</v>
+        <v>-0.08226899999999999</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>40</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.079195</v>
+        <v>-0.08008</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>41</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.076818</v>
+        <v>-0.077459</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>42</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.075784</v>
+        <v>-0.077081</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>43</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.07541299999999999</v>
+        <v>-0.07652200000000001</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>44</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.075059</v>
+        <v>-0.076264</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>45</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.074457</v>
+        <v>-0.07478700000000001</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>46</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.07248599999999999</v>
+        <v>-0.07323399999999999</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>47</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.071954</v>
+        <v>-0.073035</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>48</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.0703</v>
+        <v>-0.070857</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>49</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.069839</v>
+        <v>-0.07051200000000001</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>50</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.069192</v>
+        <v>-0.069593</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>51</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.068358</v>
+        <v>-0.069287</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>52</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.067846</v>
+        <v>-0.068732</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>53</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.067648</v>
+        <v>-0.068088</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>54</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.066382</v>
+        <v>-0.06772400000000001</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>55</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.06525599999999999</v>
+        <v>-0.065937</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>56</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.065162</v>
+        <v>-0.065751</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>57</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.06507599999999999</v>
+        <v>-0.06558600000000001</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>58</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.064663</v>
+        <v>-0.065288</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>59</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.064597</v>
+        <v>-0.06505</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>60</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.064489</v>
+        <v>-0.06468</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>61</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.06379700000000001</v>
+        <v>-0.064162</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>62</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.063504</v>
+        <v>-0.064113</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>63</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.06313199999999999</v>
+        <v>-0.06385200000000001</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>64</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.062824</v>
+        <v>-0.06379899999999999</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>65</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.062654</v>
+        <v>-0.063497</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>66</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.062566</v>
+        <v>-0.06303</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>67</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.062224</v>
+        <v>-0.062625</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>68</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.061894</v>
+        <v>-0.062077</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>69</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.061124</v>
+        <v>-0.061134</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>70</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.060131</v>
+        <v>-0.060806</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>71</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.059937</v>
+        <v>-0.060186</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>72</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.059627</v>
+        <v>-0.060082</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>73</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.059163</v>
+        <v>-0.060056</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>74</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.058142</v>
+        <v>-0.058489</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>75</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.058133</v>
+        <v>-0.058242</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>76</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.057206</v>
+        <v>-0.058189</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>77</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.056793</v>
+        <v>-0.057485</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>78</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.056672</v>
+        <v>-0.057037</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>79</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.05621</v>
+        <v>-0.05678</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>80</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.056132</v>
+        <v>-0.056593</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>81</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.055862</v>
+        <v>-0.05597</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>82</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.05542</v>
+        <v>-0.055859</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>83</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.054924</v>
+        <v>-0.055612</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>84</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.054782</v>
+        <v>-0.05499</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>85</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.054381</v>
+        <v>-0.054774</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>86</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.054152</v>
+        <v>-0.054451</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>87</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.053818</v>
+        <v>-0.054005</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>88</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.053401</v>
+        <v>-0.053893</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>89</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.053253</v>
+        <v>-0.053649</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>90</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.053193</v>
+        <v>-0.053491</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>91</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.053071</v>
+        <v>-0.053383</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>92</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.053058</v>
+        <v>-0.053319</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>93</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.052413</v>
+        <v>-0.052988</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>94</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.051773</v>
+        <v>-0.052627</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>95</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.051691</v>
+        <v>-0.051885</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>96</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.051551</v>
+        <v>-0.051877</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>97</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.05155</v>
+        <v>-0.051765</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>98</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.051267</v>
+        <v>-0.051619</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>99</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.0511</v>
+        <v>-0.051224</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>100</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.049921</v>
+        <v>-0.050425</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>101</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.049823</v>
+        <v>-0.050272</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>102</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.049815</v>
+        <v>-0.050115</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>103</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.049519</v>
+        <v>-0.049928</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>104</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.049191</v>
+        <v>-0.049485</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>105</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.04848</v>
+        <v>-0.04871</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>106</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.048369</v>
+        <v>-0.04859</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>107</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.048325</v>
+        <v>-0.048516</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>108</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.048265</v>
+        <v>-0.048507</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>109</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.047275</v>
+        <v>-0.047675</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>110</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.047243</v>
+        <v>-0.047419</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>111</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.046835</v>
+        <v>-0.047334</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>112</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.046087</v>
+        <v>-0.046609</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>113</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.045647</v>
+        <v>-0.046404</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>114</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.04562</v>
+        <v>-0.04596</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>115</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.045482</v>
+        <v>-0.045842</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>116</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.045439</v>
+        <v>-0.045835</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>117</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.045407</v>
+        <v>-0.045666</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>118</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.045125</v>
+        <v>-0.045247</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>119</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.044806</v>
+        <v>-0.045213</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>120</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.044145</v>
+        <v>-0.044197</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>121</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.043978</v>
+        <v>-0.04411</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>122</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.043209</v>
+        <v>-0.043857</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>123</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.042658</v>
+        <v>-0.042781</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>124</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.042288</v>
+        <v>-0.042485</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>125</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.042249</v>
+        <v>-0.042454</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>126</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.041966</v>
+        <v>-0.042438</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>127</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.041849</v>
+        <v>-0.042256</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>128</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.041838</v>
+        <v>-0.04222</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>129</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.041429</v>
+        <v>-0.041808</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>130</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.04133</v>
+        <v>-0.041673</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>131</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.041289</v>
+        <v>-0.041657</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>132</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.041243</v>
+        <v>-0.041643</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>133</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.041195</v>
+        <v>-0.041365</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>134</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.040604</v>
+        <v>-0.040812</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>135</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.040314</v>
+        <v>-0.040722</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>136</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.039679</v>
+        <v>-0.040262</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>137</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.039607</v>
+        <v>-0.03986</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>138</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.03956</v>
+        <v>-0.039723</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>139</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.03806</v>
+        <v>-0.038567</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>140</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.037875</v>
+        <v>-0.038353</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>141</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.037855</v>
+        <v>-0.038329</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>142</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.03772</v>
+        <v>-0.037939</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>143</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.037386</v>
+        <v>-0.037787</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>144</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.037269</v>
+        <v>-0.037654</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>145</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.037005</v>
+        <v>-0.037346</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>146</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.036643</v>
+        <v>-0.037266</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>147</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.036494</v>
+        <v>-0.036778</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>148</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.036416</v>
+        <v>-0.036596</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>149</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.0363</v>
+        <v>-0.036579</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>150</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.035954</v>
+        <v>-0.036075</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>151</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.035438</v>
+        <v>-0.035497</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>152</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.034487</v>
+        <v>-0.034843</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>153</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.034373</v>
+        <v>-0.034542</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>154</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.034295</v>
+        <v>-0.034491</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>155</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.034185</v>
+        <v>-0.034389</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>156</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.034182</v>
+        <v>-0.034379</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>157</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.034176</v>
+        <v>-0.034246</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>158</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.033473</v>
+        <v>-0.033694</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>159</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.03233</v>
+        <v>-0.032514</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>160</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.03188</v>
+        <v>-0.03196</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>161</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.031824</v>
+        <v>-0.031938</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>162</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.031733</v>
+        <v>-0.031906</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>163</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.031521</v>
+        <v>-0.031848</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>164</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.031216</v>
+        <v>-0.031756</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>165</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.031064</v>
+        <v>-0.031094</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>166</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.030942</v>
+        <v>-0.031037</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>167</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.030651</v>
+        <v>-0.030649</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>168</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.030243</v>
+        <v>-0.030437</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>169</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.029881</v>
+        <v>-0.030066</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>170</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.029504</v>
+        <v>-0.029789</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>171</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.028336</v>
+        <v>-0.028456</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>172</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.027904</v>
+        <v>-0.028289</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>173</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.027848</v>
+        <v>-0.02791</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>174</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.027464</v>
+        <v>-0.027807</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>175</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.026631</v>
+        <v>-0.027077</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>176</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.026509</v>
+        <v>-0.026715</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>177</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.026475</v>
+        <v>-0.026549</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>178</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.02646</v>
+        <v>-0.026546</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>179</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.026367</v>
+        <v>-0.026445</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>180</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.026289</v>
+        <v>-0.026381</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>181</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.025768</v>
+        <v>-0.02599</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>182</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.025545</v>
+        <v>-0.025872</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>183</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.025335</v>
+        <v>-0.025856</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>184</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.025319</v>
+        <v>-0.02576</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>185</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.025053</v>
+        <v>-0.025495</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>186</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.024965</v>
+        <v>-0.025127</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>187</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.024599</v>
+        <v>-0.02472</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>188</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.024574</v>
+        <v>-0.024711</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>189</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.024525</v>
+        <v>-0.024695</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>190</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.024498</v>
+        <v>-0.024657</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>191</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.024005</v>
+        <v>-0.024223</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>192</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.023005</v>
+        <v>-0.023377</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>193</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.022677</v>
+        <v>-0.022818</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>194</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.022256</v>
+        <v>-0.022353</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>195</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.022041</v>
+        <v>-0.022192</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>196</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.021843</v>
+        <v>-0.021883</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>197</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.021608</v>
+        <v>-0.021696</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>198</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.020787</v>
+        <v>-0.021006</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>199</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.020676</v>
+        <v>-0.020968</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>200</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.020421</v>
+        <v>-0.020909</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>201</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.02015</v>
+        <v>-0.020602</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>202</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.019344</v>
+        <v>-0.01976</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>203</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.019343</v>
+        <v>-0.019717</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>204</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.019207</v>
+        <v>-0.019497</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>205</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.019098</v>
+        <v>-0.019315</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>206</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.01897</v>
+        <v>-0.019198</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>207</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.018607</v>
+        <v>-0.019082</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>208</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.01836</v>
+        <v>-0.018732</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>209</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.018348</v>
+        <v>-0.01842</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>210</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.01826</v>
+        <v>-0.018373</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>211</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.018077</v>
+        <v>-0.018274</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>212</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.01797</v>
+        <v>-0.018202</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>213</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.017902</v>
+        <v>-0.017961</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>214</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.0179</v>
+        <v>-0.017955</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>215</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.017857</v>
+        <v>-0.017894</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>216</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.017541</v>
+        <v>-0.017642</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>217</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.017513</v>
+        <v>-0.017561</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>218</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.017374</v>
+        <v>-0.017434</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>219</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.017315</v>
+        <v>-0.017359</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>220</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.017227</v>
+        <v>-0.017331</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>221</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.016841</v>
+        <v>-0.016971</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>222</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.016733</v>
+        <v>-0.016874</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>223</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.016559</v>
+        <v>-0.016741</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>224</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.016524</v>
+        <v>-0.016662</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>225</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.016092</v>
+        <v>-0.016245</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>226</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.016045</v>
+        <v>-0.016171</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>227</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.015371</v>
+        <v>-0.01551</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>228</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.015344</v>
+        <v>-0.015408</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>229</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.015254</v>
+        <v>-0.01534</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>230</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.01511</v>
+        <v>-0.015293</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>231</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.014978</v>
+        <v>-0.015274</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>232</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.014978</v>
+        <v>-0.015175</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>233</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.014939</v>
+        <v>-0.015072</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>234</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.014641</v>
+        <v>-0.015023</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>235</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.014561</v>
+        <v>-0.015018</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>236</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.013027</v>
+        <v>-0.013241</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>237</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.012581</v>
+        <v>-0.012613</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>238</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.012329</v>
+        <v>-0.01243</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>239</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.012192</v>
+        <v>-0.012366</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>240</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.012186</v>
+        <v>-0.012219</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>241</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.01216</v>
+        <v>-0.012185</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>242</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.011938</v>
+        <v>-0.012058</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>243</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.011897</v>
+        <v>-0.011896</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>244</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.01183</v>
+        <v>-0.011855</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>245</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.011493</v>
+        <v>-0.011661</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>246</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.010775</v>
+        <v>-0.010837</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>247</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.010359</v>
+        <v>-0.010431</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>248</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.010164</v>
+        <v>-0.0102</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>249</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.010154</v>
+        <v>-0.010184</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>250</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.010099</v>
+        <v>-0.010162</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>251</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.010033</v>
+        <v>-0.010156</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>252</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.009957000000000001</v>
+        <v>-0.010079</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>253</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.009797</v>
+        <v>-0.009878</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>254</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.009736</v>
+        <v>-0.009845</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>255</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.009686</v>
+        <v>-0.009806</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>256</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.009658999999999999</v>
+        <v>-0.009767</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>257</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.00899</v>
+        <v>-0.009058999999999999</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>258</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.008946000000000001</v>
+        <v>-0.009049</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>259</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.008768</v>
+        <v>-0.008859000000000001</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>260</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.00843</v>
+        <v>-0.008473</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>261</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.00805</v>
+        <v>-0.008102</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>262</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.007697</v>
+        <v>-0.007854999999999999</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>263</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.007679</v>
+        <v>-0.007735</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>264</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.007144</v>
+        <v>-0.007172</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>265</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.006937</v>
+        <v>-0.007025</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>266</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.006808</v>
+        <v>-0.006887</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>267</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.006791</v>
+        <v>-0.006824</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>268</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.006546</v>
+        <v>-0.00658</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>269</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.006302</v>
+        <v>-0.006319</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>270</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.006113</v>
+        <v>-0.006176</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>271</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.005818</v>
+        <v>-0.005874</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>272</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.005528</v>
+        <v>-0.005596</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>273</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.00524</v>
+        <v>-0.00528</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>274</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.004921</v>
+        <v>-0.004943</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>275</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.004797</v>
+        <v>-0.004827</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>276</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.004748</v>
+        <v>-0.004777</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>277</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.004673</v>
+        <v>-0.004732</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>278</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.004655</v>
+        <v>-0.004722</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>279</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.004553</v>
+        <v>-0.004552</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>280</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.00444</v>
+        <v>-0.004456</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>281</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.004266</v>
+        <v>-0.004288</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>282</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.00387</v>
+        <v>-0.003896</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>283</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.003817</v>
+        <v>-0.003849</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>284</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.003792</v>
+        <v>-0.003799</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>285</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.003733</v>
+        <v>-0.003748</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>286</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.003426</v>
+        <v>-0.003456</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>287</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.003091</v>
+        <v>-0.003095</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>288</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.003063</v>
+        <v>-0.003079</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>289</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.002848</v>
+        <v>-0.002879</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>290</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.002207</v>
+        <v>-0.002224</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>291</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.002157</v>
+        <v>-0.002195</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>292</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.002108</v>
+        <v>-0.002144</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>293</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.00199</v>
+        <v>-0.002009</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>294</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.001984</v>
+        <v>-0.001995</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>295</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.001518</v>
+        <v>-0.001522</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>296</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.001458</v>
+        <v>-0.00147</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>297</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.001443</v>
+        <v>-0.00146</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>298</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.001145</v>
+        <v>-0.001187</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>299</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.0011</v>
+        <v>-0.001102</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>300</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.000849</v>
+        <v>-0.000888</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>301</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.000761</v>
+        <v>-0.000768</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>302</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.0006089999999999999</v>
+        <v>-0.000617</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>303</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.000516</v>
+        <v>-0.000521</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>304</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.000444</v>
+        <v>-0.000445</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>305</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.000381</v>
+        <v>-0.000382</v>
       </c>
     </row>
     <row r="994">
@@ -13352,7 +13352,7 @@
         <v>307</v>
       </c>
       <c r="C995" t="n">
-        <v>-2.4e-05</v>
+        <v>-2.5e-05</v>
       </c>
     </row>
     <row r="996">
@@ -13404,7 +13404,7 @@
         <v>311</v>
       </c>
       <c r="C999" t="n">
-        <v>0.000102</v>
+        <v>0.000103</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>312</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.000307</v>
+        <v>0.000309</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>313</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.000503</v>
+        <v>0.000504</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>314</v>
       </c>
       <c r="C1002" t="n">
-        <v>0.00102</v>
+        <v>0.001023</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>315</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.001631</v>
+        <v>0.001641</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>316</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.001849</v>
+        <v>0.001859</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>317</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.001885</v>
+        <v>0.001898</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>318</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.002077</v>
+        <v>0.002107</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>319</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.002655</v>
+        <v>0.002675</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>320</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.002798</v>
+        <v>0.002829</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>321</v>
       </c>
       <c r="C1009" t="n">
-        <v>0.003129</v>
+        <v>0.003139</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>322</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.003421</v>
+        <v>0.003453</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>323</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.004014</v>
+        <v>0.004067</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>324</v>
       </c>
       <c r="C1012" t="n">
-        <v>0.004049</v>
+        <v>0.004152</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>325</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.004162</v>
+        <v>0.004202</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>326</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.004376</v>
+        <v>0.004379</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>327</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.004698</v>
+        <v>0.004727</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>328</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.004715</v>
+        <v>0.004757</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>329</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.004717</v>
+        <v>0.004764</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>330</v>
       </c>
       <c r="C1018" t="n">
-        <v>0.004792</v>
+        <v>0.004905</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>331</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.004927</v>
+        <v>0.005007</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>332</v>
       </c>
       <c r="C1020" t="n">
-        <v>0.005237</v>
+        <v>0.005256</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>333</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.00539</v>
+        <v>0.00542</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>334</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.005401</v>
+        <v>0.005443</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>335</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.005853</v>
+        <v>0.005882</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>336</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.005855</v>
+        <v>0.00589</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>337</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.006366</v>
+        <v>0.006552</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>338</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.006759</v>
+        <v>0.006779</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>339</v>
       </c>
       <c r="C1027" t="n">
-        <v>0.007556</v>
+        <v>0.007579</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>340</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.007887</v>
+        <v>0.007972999999999999</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>341</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.008090999999999999</v>
+        <v>0.008101000000000001</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>342</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.008198</v>
+        <v>0.008219000000000001</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>343</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.008213</v>
+        <v>0.008285000000000001</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>344</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.008325000000000001</v>
+        <v>0.008363000000000001</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>345</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.008584</v>
+        <v>0.008595999999999999</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>346</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.008670000000000001</v>
+        <v>0.008699</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>347</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.008696000000000001</v>
+        <v>0.008798</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>348</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.008838</v>
+        <v>0.008947</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>349</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.009552</v>
+        <v>0.009594999999999999</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>350</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.009578</v>
+        <v>0.009639</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>351</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.009582</v>
+        <v>0.009733</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>352</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.00971</v>
+        <v>0.009756000000000001</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>353</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.009842999999999999</v>
+        <v>0.010005</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>354</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.009845</v>
+        <v>0.010012</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>355</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.009894</v>
+        <v>0.010057</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>356</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.010175</v>
+        <v>0.010209</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>357</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.010302</v>
+        <v>0.010345</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>358</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.010501</v>
+        <v>0.010564</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>359</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.010995</v>
+        <v>0.01106</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>360</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.011579</v>
+        <v>0.011615</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>361</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.011742</v>
+        <v>0.011819</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>362</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.011898</v>
+        <v>0.011921</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>363</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.011942</v>
+        <v>0.012221</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>364</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.012238</v>
+        <v>0.012257</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>365</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.012288</v>
+        <v>0.012328</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>366</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.012637</v>
+        <v>0.012916</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>367</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.012911</v>
+        <v>0.012968</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>368</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.01311</v>
+        <v>0.013139</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>369</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.013435</v>
+        <v>0.013563</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>370</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.01364</v>
+        <v>0.013722</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>371</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.013653</v>
+        <v>0.013765</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>372</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.014212</v>
+        <v>0.014247</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>373</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.014219</v>
+        <v>0.014346</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>374</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.014468</v>
+        <v>0.014559</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>375</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.014515</v>
+        <v>0.014872</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>376</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.01482</v>
+        <v>0.015136</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>377</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.015057</v>
+        <v>0.015375</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>378</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.015242</v>
+        <v>0.015533</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>379</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.015551</v>
+        <v>0.015621</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>380</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.015605</v>
+        <v>0.015719</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>381</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.015807</v>
+        <v>0.015834</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>382</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.015812</v>
+        <v>0.015849</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>383</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.016268</v>
+        <v>0.016375</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>384</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.016444</v>
+        <v>0.016566</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>385</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.016539</v>
+        <v>0.016636</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>386</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.017115</v>
+        <v>0.017188</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>387</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.017277</v>
+        <v>0.017342</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>388</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.017338</v>
+        <v>0.017487</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>389</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.017858</v>
+        <v>0.017958</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>390</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.017967</v>
+        <v>0.018059</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>391</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.01822</v>
+        <v>0.018334</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>392</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.018507</v>
+        <v>0.01853</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>393</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.018573</v>
+        <v>0.018599</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>394</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.018744</v>
+        <v>0.01895</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>395</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.018963</v>
+        <v>0.019085</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>396</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.019795</v>
+        <v>0.019822</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>397</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.020081</v>
+        <v>0.020147</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>398</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.020394</v>
+        <v>0.020656</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>399</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.021001</v>
+        <v>0.021044</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>400</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.021092</v>
+        <v>0.021199</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>401</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.021381</v>
+        <v>0.021496</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>402</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.021441</v>
+        <v>0.021614</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>403</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.02146</v>
+        <v>0.021635</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>404</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.021512</v>
+        <v>0.021716</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>405</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.022551</v>
+        <v>0.022799</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>406</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.022662</v>
+        <v>0.022832</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>407</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.022744</v>
+        <v>0.022946</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>408</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.023153</v>
+        <v>0.023224</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>409</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.023212</v>
+        <v>0.023291</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>410</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.023288</v>
+        <v>0.023574</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>411</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.023356</v>
+        <v>0.023792</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>412</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.023722</v>
+        <v>0.023874</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>413</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.024008</v>
+        <v>0.024054</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>414</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.024171</v>
+        <v>0.024441</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>415</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.024785</v>
+        <v>0.024979</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>416</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.024827</v>
+        <v>0.025105</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>417</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.024936</v>
+        <v>0.025163</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>418</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.024967</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>419</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.025068</v>
+        <v>0.025374</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>420</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.025482</v>
+        <v>0.025579</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>421</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.025736</v>
+        <v>0.025993</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>422</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.025958</v>
+        <v>0.026113</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>423</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.026223</v>
+        <v>0.026293</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>424</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.026672</v>
+        <v>0.026753</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>425</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.026682</v>
+        <v>0.026797</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>426</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.026685</v>
+        <v>0.026823</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>427</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.026725</v>
+        <v>0.026901</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>428</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.026811</v>
+        <v>0.026916</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>429</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.027014</v>
+        <v>0.027315</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>430</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.027315</v>
+        <v>0.027458</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>431</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.027652</v>
+        <v>0.027772</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>432</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.028331</v>
+        <v>0.028383</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>433</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.028362</v>
+        <v>0.028621</v>
       </c>
     </row>
     <row r="1122">
@@ -15003,7 +15003,7 @@
         <v>434</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.028919</v>
+        <v>0.029165</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>435</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.029011</v>
+        <v>0.029357</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>436</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.029333</v>
+        <v>0.029654</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>437</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.029651</v>
+        <v>0.029681</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>438</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.030432</v>
+        <v>0.030513</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>439</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.030582</v>
+        <v>0.030651</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>440</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.03084</v>
+        <v>0.031091</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>441</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.03103</v>
+        <v>0.03114</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>442</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.031347</v>
+        <v>0.031548</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>443</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.031635</v>
+        <v>0.031711</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>444</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.032457</v>
+        <v>0.03257</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>445</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.03256</v>
+        <v>0.032661</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>446</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.032611</v>
+        <v>0.032768</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>447</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.032657</v>
+        <v>0.032826</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>448</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.032713</v>
+        <v>0.032885</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>449</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.03296</v>
+        <v>0.033177</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>450</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.033098</v>
+        <v>0.033253</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>451</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.033505</v>
+        <v>0.033656</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>452</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.033512</v>
+        <v>0.033976</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>453</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.033831</v>
+        <v>0.034025</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>454</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.033849</v>
+        <v>0.034262</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>455</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.03407</v>
+        <v>0.034279</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>456</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.034308</v>
+        <v>0.034358</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>457</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.034363</v>
+        <v>0.03454</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>458</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.034589</v>
+        <v>0.034785</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>459</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.034846</v>
+        <v>0.035007</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>460</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.035044</v>
+        <v>0.035267</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>461</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.035505</v>
+        <v>0.035602</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>462</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.035755</v>
+        <v>0.035957</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>463</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.036053</v>
+        <v>0.036431</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>464</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.036614</v>
+        <v>0.037036</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>465</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.036735</v>
+        <v>0.037079</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>466</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.03694</v>
+        <v>0.037112</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>467</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.03736</v>
+        <v>0.037437</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>468</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.037384</v>
+        <v>0.037486</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>469</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.037424</v>
+        <v>0.037751</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>470</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.037477</v>
+        <v>0.03778</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>471</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.037512</v>
+        <v>0.037786</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>472</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.037789</v>
+        <v>0.038034</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>473</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.037817</v>
+        <v>0.038055</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>474</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.037854</v>
+        <v>0.038074</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>475</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.038305</v>
+        <v>0.038555</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>476</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.038561</v>
+        <v>0.038801</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>477</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.038598</v>
+        <v>0.038806</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>478</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.038709</v>
+        <v>0.038976</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>479</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.038758</v>
+        <v>0.038998</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>480</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.038812</v>
+        <v>0.039036</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>481</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.039104</v>
+        <v>0.039362</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>482</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.039326</v>
+        <v>0.039523</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>483</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.039507</v>
+        <v>0.039742</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>484</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.04032</v>
+        <v>0.040422</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>485</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.041106</v>
+        <v>0.041295</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>486</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.041151</v>
+        <v>0.041335</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>487</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.041223</v>
+        <v>0.041513</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>488</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.041289</v>
+        <v>0.041657</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>489</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.041439</v>
+        <v>0.041738</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>490</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.041725</v>
+        <v>0.042055</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>491</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.041859</v>
+        <v>0.042323</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>492</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.04222</v>
+        <v>0.042331</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>493</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.042501</v>
+        <v>0.042796</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>494</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.042556</v>
+        <v>0.042848</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>495</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.042656</v>
+        <v>0.043897</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>496</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.043746</v>
+        <v>0.044517</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>497</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.044096</v>
+        <v>0.044604</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>498</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.04418</v>
+        <v>0.044792</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>499</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.044394</v>
+        <v>0.04488</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>500</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.044743</v>
+        <v>0.045184</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>501</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.046063</v>
+        <v>0.046119</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>502</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.046069</v>
+        <v>0.046334</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>503</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.046333</v>
+        <v>0.046481</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>504</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.046381</v>
+        <v>0.046566</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>505</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.046489</v>
+        <v>0.046595</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>506</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.047133</v>
+        <v>0.0477</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>507</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.047557</v>
+        <v>0.047706</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>508</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.047665</v>
+        <v>0.047948</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>509</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.047694</v>
+        <v>0.048396</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>510</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.048177</v>
+        <v>0.048527</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>511</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.048363</v>
+        <v>0.048587</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>512</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.04874</v>
+        <v>0.048976</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>513</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.049562</v>
+        <v>0.049931</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>514</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.04982</v>
+        <v>0.050274</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>515</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.050252</v>
+        <v>0.050554</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>516</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.050856</v>
+        <v>0.050986</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>517</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.050865</v>
+        <v>0.051099</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>518</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.051296</v>
+        <v>0.051498</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>519</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.051428</v>
+        <v>0.051636</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>520</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.051806</v>
+        <v>0.05196</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>521</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.051997</v>
+        <v>0.052149</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>522</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.052056</v>
+        <v>0.052174</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>523</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.052131</v>
+        <v>0.052306</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>524</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.052233</v>
+        <v>0.052566</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>525</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.053396</v>
+        <v>0.053421</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>526</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.053713</v>
+        <v>0.054249</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>527</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.054187</v>
+        <v>0.054469</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>528</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.054452</v>
+        <v>0.054647</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>529</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.054472</v>
+        <v>0.054803</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>530</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.056192</v>
+        <v>0.05631</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>531</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.056663</v>
+        <v>0.057265</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>532</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.056973</v>
+        <v>0.057486</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>533</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.058612</v>
+        <v>0.059105</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>534</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.058652</v>
+        <v>0.059106</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>535</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.059429</v>
+        <v>0.059827</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>536</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.059609</v>
+        <v>0.059954</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>537</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.060035</v>
+        <v>0.06015</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>538</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.060241</v>
+        <v>0.060828</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>539</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.060491</v>
+        <v>0.060973</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>540</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.061036</v>
+        <v>0.061492</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>541</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.061192</v>
+        <v>0.061675</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>542</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.061397</v>
+        <v>0.061698</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>543</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.061607</v>
+        <v>0.061947</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>544</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.061785</v>
+        <v>0.062155</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>545</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.061976</v>
+        <v>0.06267399999999999</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>546</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.062158</v>
+        <v>0.06274</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>547</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.062285</v>
+        <v>0.062892</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>548</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.06265900000000001</v>
+        <v>0.06310499999999999</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>549</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.062987</v>
+        <v>0.063152</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>550</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.06304899999999999</v>
+        <v>0.06340700000000001</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>551</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.063262</v>
+        <v>0.063926</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>552</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.063774</v>
+        <v>0.064183</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>553</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.064138</v>
+        <v>0.064622</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>554</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.064482</v>
+        <v>0.065391</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>555</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.064771</v>
+        <v>0.06565799999999999</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>556</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.065068</v>
+        <v>0.06615699999999999</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>557</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.06586699999999999</v>
+        <v>0.066275</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>558</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.06605</v>
+        <v>0.06665699999999999</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>559</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.066358</v>
+        <v>0.066718</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>560</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.066555</v>
+        <v>0.066894</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>561</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.06693300000000001</v>
+        <v>0.068062</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>562</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.067597</v>
+        <v>0.06837699999999999</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>563</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.067853</v>
+        <v>0.06851</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>564</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.067968</v>
+        <v>0.068568</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>565</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.068048</v>
+        <v>0.06929299999999999</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>566</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.069186</v>
+        <v>0.06981</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>567</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.06936199999999999</v>
+        <v>0.06990399999999999</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>568</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.07008300000000001</v>
+        <v>0.070462</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>569</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.070171</v>
+        <v>0.07062</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>570</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.07036100000000001</v>
+        <v>0.070713</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>571</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.07054299999999999</v>
+        <v>0.07081899999999999</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>572</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.071228</v>
+        <v>0.071283</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>573</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.071787</v>
+        <v>0.072476</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>574</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.07258299999999999</v>
+        <v>0.07283100000000001</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>575</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.072865</v>
+        <v>0.073282</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>576</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.073088</v>
+        <v>0.073453</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>577</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.074283</v>
+        <v>0.074906</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>578</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.07442600000000001</v>
+        <v>0.075296</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>579</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.07463400000000001</v>
+        <v>0.075886</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>580</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.074896</v>
+        <v>0.07615</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>581</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.07623099999999999</v>
+        <v>0.076526</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>582</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.076753</v>
+        <v>0.076887</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>583</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.076774</v>
+        <v>0.07710500000000001</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>584</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.079154</v>
+        <v>0.07987900000000001</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>585</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.079251</v>
+        <v>0.08000699999999999</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>586</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.080453</v>
+        <v>0.08071399999999999</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>587</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.080677</v>
+        <v>0.080946</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>588</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.08074199999999999</v>
+        <v>0.08137900000000001</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>589</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.080849</v>
+        <v>0.08161499999999999</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>590</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.082042</v>
+        <v>0.0824</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>591</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.08221299999999999</v>
+        <v>0.083053</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>592</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.08289100000000001</v>
+        <v>0.083201</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>593</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.082899</v>
+        <v>0.08387500000000001</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>594</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.08323999999999999</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>595</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.084049</v>
+        <v>0.084425</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>596</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.08409</v>
+        <v>0.08463</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>597</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.084401</v>
+        <v>0.085004</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>598</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.084886</v>
+        <v>0.085185</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>599</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.08602600000000001</v>
+        <v>0.086906</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>600</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.086852</v>
+        <v>0.08698599999999999</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>601</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.0873</v>
+        <v>0.087474</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>602</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.087301</v>
+        <v>0.087716</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>603</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.087466</v>
+        <v>0.08802</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>604</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.08747099999999999</v>
+        <v>0.088958</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>605</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.08803900000000001</v>
+        <v>0.089104</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>606</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.088073</v>
+        <v>0.089249</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>607</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.090269</v>
+        <v>0.09063499999999999</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>608</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.09045</v>
+        <v>0.090902</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>609</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.091068</v>
+        <v>0.091964</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>610</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.091833</v>
+        <v>0.092474</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>611</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.09188300000000001</v>
+        <v>0.09306499999999999</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>612</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.09278699999999999</v>
+        <v>0.094267</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>613</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.093709</v>
+        <v>0.094307</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>614</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.094194</v>
+        <v>0.09436799999999999</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>615</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.09460499999999999</v>
+        <v>0.094981</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>616</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.095223</v>
+        <v>0.09550500000000001</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>617</v>
       </c>
       <c r="C1305" t="n">
-        <v>0.09707200000000001</v>
+        <v>0.097443</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>618</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.09715</v>
+        <v>0.097576</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>619</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.100291</v>
+        <v>0.10056</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>620</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.101921</v>
+        <v>0.102206</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>621</v>
       </c>
       <c r="C1309" t="n">
-        <v>0.102166</v>
+        <v>0.103992</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>622</v>
       </c>
       <c r="C1310" t="n">
-        <v>0.104146</v>
+        <v>0.104526</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>623</v>
       </c>
       <c r="C1311" t="n">
-        <v>0.104443</v>
+        <v>0.105089</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>624</v>
       </c>
       <c r="C1312" t="n">
-        <v>0.105048</v>
+        <v>0.105283</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>625</v>
       </c>
       <c r="C1313" t="n">
-        <v>0.106714</v>
+        <v>0.107938</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>626</v>
       </c>
       <c r="C1314" t="n">
-        <v>0.106849</v>
+        <v>0.108433</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>627</v>
       </c>
       <c r="C1315" t="n">
-        <v>0.108285</v>
+        <v>0.108788</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>628</v>
       </c>
       <c r="C1316" t="n">
-        <v>0.109845</v>
+        <v>0.110905</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>629</v>
       </c>
       <c r="C1317" t="n">
-        <v>0.110587</v>
+        <v>0.111574</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>630</v>
       </c>
       <c r="C1318" t="n">
-        <v>0.111572</v>
+        <v>0.112195</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>631</v>
       </c>
       <c r="C1319" t="n">
-        <v>0.113289</v>
+        <v>0.113543</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>632</v>
       </c>
       <c r="C1320" t="n">
-        <v>0.114655</v>
+        <v>0.114797</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>633</v>
       </c>
       <c r="C1321" t="n">
-        <v>0.115883</v>
+        <v>0.116567</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>634</v>
       </c>
       <c r="C1322" t="n">
-        <v>0.116057</v>
+        <v>0.116761</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>635</v>
       </c>
       <c r="C1323" t="n">
-        <v>0.116307</v>
+        <v>0.117243</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>636</v>
       </c>
       <c r="C1324" t="n">
-        <v>0.117176</v>
+        <v>0.117797</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>637</v>
       </c>
       <c r="C1325" t="n">
-        <v>0.117591</v>
+        <v>0.118039</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>638</v>
       </c>
       <c r="C1326" t="n">
-        <v>0.11767</v>
+        <v>0.119262</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>639</v>
       </c>
       <c r="C1327" t="n">
-        <v>0.118465</v>
+        <v>0.119439</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>640</v>
       </c>
       <c r="C1328" t="n">
-        <v>0.119059</v>
+        <v>0.119873</v>
       </c>
     </row>
     <row r="1329">
@@ -17694,7 +17694,7 @@
         <v>641</v>
       </c>
       <c r="C1329" t="n">
-        <v>0.121802</v>
+        <v>0.122986</v>
       </c>
     </row>
     <row r="1330">
@@ -17707,7 +17707,7 @@
         <v>642</v>
       </c>
       <c r="C1330" t="n">
-        <v>0.122267</v>
+        <v>0.12344</v>
       </c>
     </row>
     <row r="1331">
@@ -17720,7 +17720,7 @@
         <v>643</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.12304</v>
+        <v>0.124248</v>
       </c>
     </row>
     <row r="1332">
@@ -17733,7 +17733,7 @@
         <v>644</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.125468</v>
+        <v>0.126154</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>645</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.126527</v>
+        <v>0.12781</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>646</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.127412</v>
+        <v>0.127819</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>647</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.127703</v>
+        <v>0.128916</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>648</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.129269</v>
+        <v>0.130024</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>649</v>
       </c>
       <c r="C1337" t="n">
-        <v>0.130597</v>
+        <v>0.130967</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>650</v>
       </c>
       <c r="C1338" t="n">
-        <v>0.131202</v>
+        <v>0.131323</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>651</v>
       </c>
       <c r="C1339" t="n">
-        <v>0.131362</v>
+        <v>0.13169</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>652</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.132383</v>
+        <v>0.133358</v>
       </c>
     </row>
     <row r="1341">
@@ -17850,7 +17850,7 @@
         <v>653</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.13263</v>
+        <v>0.133507</v>
       </c>
     </row>
     <row r="1342">
@@ -17863,7 +17863,7 @@
         <v>654</v>
       </c>
       <c r="C1342" t="n">
-        <v>0.136914</v>
+        <v>0.137073</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>655</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.143549</v>
+        <v>0.146166</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>656</v>
       </c>
       <c r="C1344" t="n">
-        <v>0.144253</v>
+        <v>0.147565</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>657</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.149441</v>
+        <v>0.149889</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>658</v>
       </c>
       <c r="C1346" t="n">
-        <v>0.150255</v>
+        <v>0.151093</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>659</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.152307</v>
+        <v>0.152887</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>660</v>
       </c>
       <c r="C1348" t="n">
-        <v>0.15474</v>
+        <v>0.158037</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>661</v>
       </c>
       <c r="C1349" t="n">
-        <v>0.156823</v>
+        <v>0.158408</v>
       </c>
     </row>
     <row r="1350">
@@ -17967,7 +17967,7 @@
         <v>662</v>
       </c>
       <c r="C1350" t="n">
-        <v>0.157804</v>
+        <v>0.159013</v>
       </c>
     </row>
     <row r="1351">
@@ -17980,7 +17980,7 @@
         <v>663</v>
       </c>
       <c r="C1351" t="n">
-        <v>0.159124</v>
+        <v>0.16111</v>
       </c>
     </row>
     <row r="1352">
@@ -17993,7 +17993,7 @@
         <v>664</v>
       </c>
       <c r="C1352" t="n">
-        <v>0.162965</v>
+        <v>0.163852</v>
       </c>
     </row>
     <row r="1353">
@@ -18006,7 +18006,7 @@
         <v>665</v>
       </c>
       <c r="C1353" t="n">
-        <v>0.164139</v>
+        <v>0.165874</v>
       </c>
     </row>
     <row r="1354">
@@ -18019,7 +18019,7 @@
         <v>666</v>
       </c>
       <c r="C1354" t="n">
-        <v>0.166078</v>
+        <v>0.166506</v>
       </c>
     </row>
     <row r="1355">
@@ -18032,7 +18032,7 @@
         <v>667</v>
       </c>
       <c r="C1355" t="n">
-        <v>0.169314</v>
+        <v>0.169646</v>
       </c>
     </row>
     <row r="1356">
@@ -18045,7 +18045,7 @@
         <v>668</v>
       </c>
       <c r="C1356" t="n">
-        <v>0.172443</v>
+        <v>0.174797</v>
       </c>
     </row>
     <row r="1357">
@@ -18058,7 +18058,7 @@
         <v>669</v>
       </c>
       <c r="C1357" t="n">
-        <v>0.174893</v>
+        <v>0.17631</v>
       </c>
     </row>
     <row r="1358">
@@ -18071,7 +18071,7 @@
         <v>670</v>
       </c>
       <c r="C1358" t="n">
-        <v>0.17575</v>
+        <v>0.178845</v>
       </c>
     </row>
     <row r="1359">
@@ -18084,7 +18084,7 @@
         <v>671</v>
       </c>
       <c r="C1359" t="n">
-        <v>0.177768</v>
+        <v>0.180465</v>
       </c>
     </row>
     <row r="1360">
@@ -18097,7 +18097,7 @@
         <v>672</v>
       </c>
       <c r="C1360" t="n">
-        <v>0.188087</v>
+        <v>0.18879</v>
       </c>
     </row>
     <row r="1361">
@@ -18110,7 +18110,7 @@
         <v>673</v>
       </c>
       <c r="C1361" t="n">
-        <v>0.191645</v>
+        <v>0.193711</v>
       </c>
     </row>
     <row r="1362">
@@ -18123,7 +18123,7 @@
         <v>674</v>
       </c>
       <c r="C1362" t="n">
-        <v>0.196529</v>
+        <v>0.202325</v>
       </c>
     </row>
     <row r="1363">
@@ -18136,7 +18136,7 @@
         <v>675</v>
       </c>
       <c r="C1363" t="n">
-        <v>0.202009</v>
+        <v>0.206049</v>
       </c>
     </row>
     <row r="1364">
@@ -18149,7 +18149,7 @@
         <v>676</v>
       </c>
       <c r="C1364" t="n">
-        <v>0.211973</v>
+        <v>0.215387</v>
       </c>
     </row>
     <row r="1365">
@@ -18162,7 +18162,7 @@
         <v>677</v>
       </c>
       <c r="C1365" t="n">
-        <v>0.222911</v>
+        <v>0.223697</v>
       </c>
     </row>
     <row r="1366">
@@ -18175,7 +18175,7 @@
         <v>678</v>
       </c>
       <c r="C1366" t="n">
-        <v>0.223629</v>
+        <v>0.225171</v>
       </c>
     </row>
     <row r="1367">
@@ -18188,7 +18188,7 @@
         <v>679</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.230509</v>
+        <v>0.232207</v>
       </c>
     </row>
     <row r="1368">
@@ -18201,7 +18201,7 @@
         <v>680</v>
       </c>
       <c r="C1368" t="n">
-        <v>0.247289</v>
+        <v>0.248446</v>
       </c>
     </row>
     <row r="1369">
@@ -18214,7 +18214,7 @@
         <v>681</v>
       </c>
       <c r="C1369" t="n">
-        <v>0.276518</v>
+        <v>0.278184</v>
       </c>
     </row>
     <row r="1370">
@@ -18227,7 +18227,7 @@
         <v>682</v>
       </c>
       <c r="C1370" t="n">
-        <v>0.277584</v>
+        <v>0.279905</v>
       </c>
     </row>
     <row r="1371">
@@ -18240,7 +18240,7 @@
         <v>683</v>
       </c>
       <c r="C1371" t="n">
-        <v>0.3128</v>
+        <v>0.313884</v>
       </c>
     </row>
     <row r="1372">
@@ -18253,7 +18253,7 @@
         <v>684</v>
       </c>
       <c r="C1372" t="n">
-        <v>0.347132</v>
+        <v>0.351465</v>
       </c>
     </row>
     <row r="1373">
@@ -18266,7 +18266,7 @@
         <v>685</v>
       </c>
       <c r="C1373" t="n">
-        <v>0.403327</v>
+        <v>0.407638</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.256353</v>
+        <v>-0.258537</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.240094</v>
+        <v>-0.235478</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>2</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.234192</v>
+        <v>-0.23515</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>3</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.225856</v>
+        <v>-0.2277</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>4</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.223756</v>
+        <v>-0.224969</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>5</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.210354</v>
+        <v>-0.212076</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>6</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.173864</v>
+        <v>-0.173205</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>7</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.141254</v>
+        <v>-0.141652</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>8</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.131867</v>
+        <v>-0.128634</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>9</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.129742</v>
+        <v>-0.127161</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>10</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.12175</v>
+        <v>-0.120744</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>11</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.119852</v>
+        <v>-0.120615</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>12</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.119781</v>
+        <v>-0.120399</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>13</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.118036</v>
+        <v>-0.115691</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>14</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.115181</v>
+        <v>-0.114009</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>15</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.113624</v>
+        <v>-0.113308</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.112984</v>
+        <v>-0.112794</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>17</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.111306</v>
+        <v>-0.111568</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>18</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.109071</v>
+        <v>-0.108494</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>19</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.107816</v>
+        <v>-0.107419</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>20</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.105611</v>
+        <v>-0.105315</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.104775</v>
+        <v>-0.104356</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>22</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.104345</v>
+        <v>-0.103152</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>23</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.102046</v>
+        <v>-0.101983</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>24</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.101191</v>
+        <v>-0.101141</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>25</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.100433</v>
+        <v>-0.100472</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>26</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.099951</v>
+        <v>-0.09983499999999999</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>27</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.099619</v>
+        <v>-0.09859800000000001</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>28</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.097982</v>
+        <v>-0.097867</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>29</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.09790500000000001</v>
+        <v>-0.097646</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>30</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.097779</v>
+        <v>-0.097302</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>31</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.097168</v>
+        <v>-0.096632</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>32</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.096292</v>
+        <v>-0.096497</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>33</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.095833</v>
+        <v>-0.095744</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>34</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.09576900000000001</v>
+        <v>-0.095694</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>35</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.09563000000000001</v>
+        <v>-0.09503200000000001</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>36</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.094763</v>
+        <v>-0.094976</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>37</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.090935</v>
+        <v>-0.091388</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>38</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.090808</v>
+        <v>-0.090463</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>39</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.090528</v>
+        <v>-0.090027</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>40</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.090087</v>
+        <v>-0.08923200000000001</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>41</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.08870500000000001</v>
+        <v>-0.08817800000000001</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>42</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.084735</v>
+        <v>-0.085503</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>43</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.084687</v>
+        <v>-0.08473799999999999</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>44</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.084096</v>
+        <v>-0.084659</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>45</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.083977</v>
+        <v>-0.08397399999999999</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>46</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.082371</v>
+        <v>-0.08137800000000001</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>47</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.08230899999999999</v>
+        <v>-0.081159</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>48</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.081179</v>
+        <v>-0.081029</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>49</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.08043</v>
+        <v>-0.08097799999999999</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>50</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.080424</v>
+        <v>-0.080182</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>51</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.078262</v>
+        <v>-0.078972</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>52</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.077116</v>
+        <v>-0.077796</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>53</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.077097</v>
+        <v>-0.07757799999999999</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>54</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.076417</v>
+        <v>-0.07647900000000001</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>55</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.07595300000000001</v>
+        <v>-0.076251</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>56</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.07593900000000001</v>
+        <v>-0.075726</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>57</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.075699</v>
+        <v>-0.075487</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>58</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.074906</v>
+        <v>-0.07519000000000001</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>59</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.07403</v>
+        <v>-0.074562</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>60</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.073475</v>
+        <v>-0.0733</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>61</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.073184</v>
+        <v>-0.072439</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>62</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.072022</v>
+        <v>-0.07238799999999999</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>63</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.070701</v>
+        <v>-0.070497</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>64</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.070144</v>
+        <v>-0.06951</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>65</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.06931</v>
+        <v>-0.068837</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>66</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.068804</v>
+        <v>-0.068551</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>67</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.068102</v>
+        <v>-0.068051</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>68</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.06750299999999999</v>
+        <v>-0.06794799999999999</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>69</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.06725</v>
+        <v>-0.067569</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>70</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.067218</v>
+        <v>-0.06718399999999999</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>71</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.066964</v>
+        <v>-0.067123</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>72</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.066051</v>
+        <v>-0.066639</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>73</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.065863</v>
+        <v>-0.066345</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>74</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.065806</v>
+        <v>-0.065096</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>75</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.065308</v>
+        <v>-0.064459</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>76</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.064461</v>
+        <v>-0.064037</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>77</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.063607</v>
+        <v>-0.06386600000000001</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>78</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.063475</v>
+        <v>-0.063442</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>79</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.06340899999999999</v>
+        <v>-0.062752</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>80</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.062804</v>
+        <v>-0.062706</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>81</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.062169</v>
+        <v>-0.062487</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>82</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.062051</v>
+        <v>-0.062348</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>83</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.06168</v>
+        <v>-0.062204</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>84</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.06147</v>
+        <v>-0.062027</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>85</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.061333</v>
+        <v>-0.061279</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>86</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.06124</v>
+        <v>-0.061146</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>87</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.061089</v>
+        <v>-0.061028</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>88</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.060956</v>
+        <v>-0.060533</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>89</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.060905</v>
+        <v>-0.060281</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>90</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.060224</v>
+        <v>-0.06021</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>91</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.059918</v>
+        <v>-0.059782</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>92</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.059749</v>
+        <v>-0.059407</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>93</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.059285</v>
+        <v>-0.059212</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>94</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.059269</v>
+        <v>-0.058545</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>95</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.058358</v>
+        <v>-0.058354</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>96</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.057912</v>
+        <v>-0.058311</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>97</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.057855</v>
+        <v>-0.057499</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>98</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.057412</v>
+        <v>-0.057376</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>99</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.057122</v>
+        <v>-0.057274</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>100</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.056957</v>
+        <v>-0.05717</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>101</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.056502</v>
+        <v>-0.056635</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>102</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.055149</v>
+        <v>-0.05505</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>103</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.054332</v>
+        <v>-0.054601</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>104</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.054162</v>
+        <v>-0.053846</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>105</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.05413</v>
+        <v>-0.053665</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>106</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.053831</v>
+        <v>-0.053646</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>107</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.053445</v>
+        <v>-0.053385</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>108</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.053389</v>
+        <v>-0.053128</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>109</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.053116</v>
+        <v>-0.052939</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>110</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.053111</v>
+        <v>-0.052526</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>111</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.052825</v>
+        <v>-0.052525</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>112</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.052598</v>
+        <v>-0.052492</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>113</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.052293</v>
+        <v>-0.052477</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>114</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.052177</v>
+        <v>-0.052101</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>115</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.0521</v>
+        <v>-0.051881</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>116</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.051617</v>
+        <v>-0.051583</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>117</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.051421</v>
+        <v>-0.051542</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>118</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.051327</v>
+        <v>-0.05117</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>119</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.051097</v>
+        <v>-0.050664</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>120</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.05045</v>
+        <v>-0.049862</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>121</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.04956</v>
+        <v>-0.049197</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>122</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.048782</v>
+        <v>-0.049011</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>123</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.048612</v>
+        <v>-0.048853</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>124</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.048509</v>
+        <v>-0.048577</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>125</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.048376</v>
+        <v>-0.04809</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>126</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.0479</v>
+        <v>-0.048007</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>127</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.047382</v>
+        <v>-0.04777</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>128</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.046921</v>
+        <v>-0.04715</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>129</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.046781</v>
+        <v>-0.047072</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>130</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.046413</v>
+        <v>-0.046551</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>131</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.046298</v>
+        <v>-0.046513</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>132</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.046135</v>
+        <v>-0.046243</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>133</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.046051</v>
+        <v>-0.046118</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>134</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.045958</v>
+        <v>-0.045887</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>135</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.045669</v>
+        <v>-0.045636</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>136</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.045583</v>
+        <v>-0.045584</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>137</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.044891</v>
+        <v>-0.044673</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>138</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.04431</v>
+        <v>-0.044347</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>139</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.044285</v>
+        <v>-0.044254</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>140</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.043883</v>
+        <v>-0.043483</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>141</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.04328</v>
+        <v>-0.043347</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>142</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.043159</v>
+        <v>-0.043325</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>143</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.042975</v>
+        <v>-0.043309</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>144</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.04292</v>
+        <v>-0.043134</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>145</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.042576</v>
+        <v>-0.042773</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>146</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.042455</v>
+        <v>-0.0426</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>147</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.042238</v>
+        <v>-0.042454</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>148</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.042167</v>
+        <v>-0.041721</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>149</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.041962</v>
+        <v>-0.041219</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>150</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.040016</v>
+        <v>-0.040091</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>151</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.039974</v>
+        <v>-0.039929</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>152</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.039784</v>
+        <v>-0.039843</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>153</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.039767</v>
+        <v>-0.039514</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>154</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.039599</v>
+        <v>-0.039394</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>155</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.039484</v>
+        <v>-0.039255</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>156</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.038705</v>
+        <v>-0.038541</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>157</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.037727</v>
+        <v>-0.037454</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>158</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.037169</v>
+        <v>-0.037321</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>159</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.037037</v>
+        <v>-0.037199</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>160</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.035808</v>
+        <v>-0.03604</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>161</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.034831</v>
+        <v>-0.035143</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>162</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.034804</v>
+        <v>-0.034909</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>163</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.034762</v>
+        <v>-0.034888</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>164</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.03467</v>
+        <v>-0.034559</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>165</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.033978</v>
+        <v>-0.034257</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>166</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.033766</v>
+        <v>-0.033749</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>167</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.033627</v>
+        <v>-0.033714</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>168</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.033412</v>
+        <v>-0.033427</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>169</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.032976</v>
+        <v>-0.033158</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>170</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.031808</v>
+        <v>-0.031941</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>171</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.031768</v>
+        <v>-0.03185</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>172</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.031746</v>
+        <v>-0.031331</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>173</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.03105</v>
+        <v>-0.031328</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>174</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.031046</v>
+        <v>-0.031081</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>175</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.030888</v>
+        <v>-0.031024</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>176</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.029819</v>
+        <v>-0.029848</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>177</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.029815</v>
+        <v>-0.029758</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>178</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.029809</v>
+        <v>-0.029702</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>179</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.029671</v>
+        <v>-0.029403</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>180</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.029639</v>
+        <v>-0.029074</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>181</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.02892</v>
+        <v>-0.029033</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>182</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.028834</v>
+        <v>-0.028998</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>183</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.028687</v>
+        <v>-0.028878</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>184</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.028659</v>
+        <v>-0.028586</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>185</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.028638</v>
+        <v>-0.028555</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>186</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.028494</v>
+        <v>-0.028427</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>187</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.028381</v>
+        <v>-0.028317</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>188</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.028196</v>
+        <v>-0.027848</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>189</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.02764</v>
+        <v>-0.027841</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>190</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.027582</v>
+        <v>-0.027785</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>191</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.027312</v>
+        <v>-0.027354</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>192</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.027151</v>
+        <v>-0.027332</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>193</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.026658</v>
+        <v>-0.026668</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>194</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.026344</v>
+        <v>-0.026324</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>195</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.026174</v>
+        <v>-0.026265</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>196</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.026063</v>
+        <v>-0.026022</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>197</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.025547</v>
+        <v>-0.025436</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>198</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.025116</v>
+        <v>-0.024981</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>199</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.024914</v>
+        <v>-0.024868</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>200</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.024211</v>
+        <v>-0.024197</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>201</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.023856</v>
+        <v>-0.023405</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>202</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.022851</v>
+        <v>-0.022962</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>203</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.022815</v>
+        <v>-0.022948</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>204</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.022222</v>
+        <v>-0.022157</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>205</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.022203</v>
+        <v>-0.021945</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>206</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.021495</v>
+        <v>-0.021442</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>207</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.021432</v>
+        <v>-0.021359</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>208</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.021348</v>
+        <v>-0.021203</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>209</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.02106</v>
+        <v>-0.020995</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>210</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.020864</v>
+        <v>-0.020959</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>211</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.020355</v>
+        <v>-0.020312</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>212</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.020337</v>
+        <v>-0.02027</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>213</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.02018</v>
+        <v>-0.020209</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>214</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.019605</v>
+        <v>-0.019571</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>215</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.019451</v>
+        <v>-0.01936</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>216</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.019323</v>
+        <v>-0.019211</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>217</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.019191</v>
+        <v>-0.019146</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>218</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.019114</v>
+        <v>-0.019129</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>219</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.01907</v>
+        <v>-0.019122</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>220</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.018914</v>
+        <v>-0.018888</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>221</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.018895</v>
+        <v>-0.01884</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>222</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.018745</v>
+        <v>-0.018763</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>223</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.018652</v>
+        <v>-0.018656</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>224</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.018494</v>
+        <v>-0.018652</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>225</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.018309</v>
+        <v>-0.018223</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>226</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.018079</v>
+        <v>-0.018206</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>227</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.017834</v>
+        <v>-0.017913</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>228</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.017371</v>
+        <v>-0.017346</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>229</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.016751</v>
+        <v>-0.01684</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>230</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.016316</v>
+        <v>-0.016381</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>231</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.016107</v>
+        <v>-0.016106</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>232</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.015967</v>
+        <v>-0.016082</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>233</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.015306</v>
+        <v>-0.01524</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>234</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.013788</v>
+        <v>-0.013837</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>235</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.013713</v>
+        <v>-0.013743</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>236</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.013622</v>
+        <v>-0.013601</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>237</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.013461</v>
+        <v>-0.013387</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>238</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.013415</v>
+        <v>-0.013197</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>239</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.013198</v>
+        <v>-0.013133</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>240</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.012965</v>
+        <v>-0.012994</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>241</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.012516</v>
+        <v>-0.012498</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>242</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.012196</v>
+        <v>-0.012254</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>243</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.012043</v>
+        <v>-0.012071</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>244</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.011681</v>
+        <v>-0.011733</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>245</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.011435</v>
+        <v>-0.011388</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>246</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.011395</v>
+        <v>-0.011223</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>247</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.011047</v>
+        <v>-0.011139</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>248</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.010927</v>
+        <v>-0.010888</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>249</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.010804</v>
+        <v>-0.010814</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>250</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.010802</v>
+        <v>-0.010798</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>251</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.010622</v>
+        <v>-0.010717</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>252</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.01027</v>
+        <v>-0.010316</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>253</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.010156</v>
+        <v>-0.010078</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>254</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.010008</v>
+        <v>-0.010056</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>255</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.009988</v>
+        <v>-0.009835</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>256</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.009169999999999999</v>
+        <v>-0.009096999999999999</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>257</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.009136</v>
+        <v>-0.009050000000000001</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>258</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.008840000000000001</v>
+        <v>-0.008887000000000001</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>259</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.008739</v>
+        <v>-0.008793</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>260</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.008669</v>
+        <v>-0.008723</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>261</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.00865</v>
+        <v>-0.008702</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>262</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.008226000000000001</v>
+        <v>-0.008229</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>263</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.007757</v>
+        <v>-0.007767</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>264</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.007498</v>
+        <v>-0.007553</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>265</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.007497</v>
+        <v>-0.007468</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>266</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.007305</v>
+        <v>-0.007325</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>267</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.006853</v>
+        <v>-0.006883</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>268</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.006819</v>
+        <v>-0.006866</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>269</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.006781</v>
+        <v>-0.006805</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>270</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.006425</v>
+        <v>-0.006353</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>271</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.006352</v>
+        <v>-0.006293</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>272</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.005514</v>
+        <v>-0.005537</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>273</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.005513</v>
+        <v>-0.00553</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>274</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.005481</v>
+        <v>-0.005443</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>275</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.005385</v>
+        <v>-0.005299</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>276</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.005251</v>
+        <v>-0.005272</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>277</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.004793</v>
+        <v>-0.004773</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>278</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.0046</v>
+        <v>-0.004615</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>279</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.004554</v>
+        <v>-0.004588</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>280</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.004375</v>
+        <v>-0.004402</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>281</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.004149</v>
+        <v>-0.004162</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>282</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.004041</v>
+        <v>-0.004065</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>283</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.003955</v>
+        <v>-0.003975</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>284</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.003912</v>
+        <v>-0.003947</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>285</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.003357</v>
+        <v>-0.00333</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>286</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.003231</v>
+        <v>-0.003201</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>287</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.003187</v>
+        <v>-0.003173</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>288</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.002537</v>
+        <v>-0.002546</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>289</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.002524</v>
+        <v>-0.002542</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>290</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.002519</v>
+        <v>-0.002529</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>291</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.002177</v>
+        <v>-0.002158</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>292</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.00175</v>
+        <v>-0.001733</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>293</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.001672</v>
+        <v>-0.001661</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>294</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.001659</v>
+        <v>-0.001639</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>295</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.001555</v>
+        <v>-0.001567</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>296</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.001224</v>
+        <v>-0.001232</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>297</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.00118</v>
+        <v>-0.001184</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>298</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.000953</v>
+        <v>-0.000954</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>299</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.000712</v>
+        <v>-0.000697</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>300</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.000623</v>
+        <v>-0.000627</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>301</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.000457</v>
+        <v>-0.000459</v>
       </c>
     </row>
     <row r="978">
@@ -13196,7 +13196,7 @@
         <v>307</v>
       </c>
       <c r="C983" t="n">
-        <v>0.000115</v>
+        <v>0.000114</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>308</v>
       </c>
       <c r="C984" t="n">
-        <v>0.000339</v>
+        <v>0.000341</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>309</v>
       </c>
       <c r="C985" t="n">
-        <v>0.000545</v>
+        <v>0.000544</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>310</v>
       </c>
       <c r="C986" t="n">
-        <v>0.001109</v>
+        <v>0.00111</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>311</v>
       </c>
       <c r="C987" t="n">
-        <v>0.001755</v>
+        <v>0.001769</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>312</v>
       </c>
       <c r="C988" t="n">
-        <v>0.002084</v>
+        <v>0.002068</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>313</v>
       </c>
       <c r="C989" t="n">
-        <v>0.00215</v>
+        <v>0.002163</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>314</v>
       </c>
       <c r="C990" t="n">
-        <v>0.002341</v>
+        <v>0.002363</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>315</v>
       </c>
       <c r="C991" t="n">
-        <v>0.002477</v>
+        <v>0.002496</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>316</v>
       </c>
       <c r="C992" t="n">
-        <v>0.003145</v>
+        <v>0.003158</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>317</v>
       </c>
       <c r="C993" t="n">
-        <v>0.003149</v>
+        <v>0.003176</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>318</v>
       </c>
       <c r="C994" t="n">
-        <v>0.003426</v>
+        <v>0.003434</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>319</v>
       </c>
       <c r="C995" t="n">
-        <v>0.003634</v>
+        <v>0.003667</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>320</v>
       </c>
       <c r="C996" t="n">
-        <v>0.004504</v>
+        <v>0.00451</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>321</v>
       </c>
       <c r="C997" t="n">
-        <v>0.004566</v>
+        <v>0.004575</v>
       </c>
     </row>
     <row r="998">
@@ -13391,7 +13391,7 @@
         <v>322</v>
       </c>
       <c r="C998" t="n">
-        <v>0.005056</v>
+        <v>0.005065</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>323</v>
       </c>
       <c r="C999" t="n">
-        <v>0.005058</v>
+        <v>0.005097</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>324</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.005091</v>
+        <v>0.005135</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>325</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.005147</v>
+        <v>0.005164</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>326</v>
       </c>
       <c r="C1002" t="n">
-        <v>0.005323</v>
+        <v>0.005289</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>327</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.005401</v>
+        <v>0.005368</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>328</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.005442</v>
+        <v>0.005488</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>329</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.005633</v>
+        <v>0.00565</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>330</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.005683</v>
+        <v>0.005663</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>331</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.006314</v>
+        <v>0.006356</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>332</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.006577</v>
+        <v>0.00661</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>333</v>
       </c>
       <c r="C1009" t="n">
-        <v>0.006674</v>
+        <v>0.006708</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>334</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.007328</v>
+        <v>0.007348</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>335</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.008163999999999999</v>
+        <v>0.008219000000000001</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>336</v>
       </c>
       <c r="C1012" t="n">
-        <v>0.008189999999999999</v>
+        <v>0.008238000000000001</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>337</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.008462000000000001</v>
+        <v>0.008538</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>338</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.008697999999999999</v>
+        <v>0.008742</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>339</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.008959</v>
+        <v>0.008954999999999999</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>340</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.009088000000000001</v>
+        <v>0.008997</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>341</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.009175000000000001</v>
+        <v>0.009256</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>342</v>
       </c>
       <c r="C1018" t="n">
-        <v>0.009303000000000001</v>
+        <v>0.009259999999999999</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>343</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>344</v>
       </c>
       <c r="C1020" t="n">
-        <v>0.00991</v>
+        <v>0.00976</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>345</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.010231</v>
+        <v>0.010318</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>346</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.010453</v>
+        <v>0.010531</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>347</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.01046</v>
+        <v>0.010547</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>348</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.01097</v>
+        <v>0.011021</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>349</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.011207</v>
+        <v>0.01121</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>350</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.011326</v>
+        <v>0.011271</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>351</v>
       </c>
       <c r="C1027" t="n">
-        <v>0.011528</v>
+        <v>0.01131</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>352</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.011814</v>
+        <v>0.011921</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>353</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.012126</v>
+        <v>0.012032</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>354</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.012145</v>
+        <v>0.012166</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>355</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.012466</v>
+        <v>0.012484</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>356</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.012558</v>
+        <v>0.012522</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>357</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.012629</v>
+        <v>0.012632</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>358</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.012884</v>
+        <v>0.01292</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>359</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.012969</v>
+        <v>0.013064</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>360</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.013243</v>
+        <v>0.013286</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>361</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.013328</v>
+        <v>0.013326</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>362</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.013576</v>
+        <v>0.013691</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>363</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.013817</v>
+        <v>0.013911</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>364</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.014039</v>
+        <v>0.014065</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>365</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.015057</v>
+        <v>0.01504</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>366</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.015277</v>
+        <v>0.015051</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>367</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.015284</v>
+        <v>0.015243</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>368</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.015663</v>
+        <v>0.015645</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>369</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.01582</v>
+        <v>0.01596</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>370</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.015952</v>
+        <v>0.015963</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>371</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.016029</v>
+        <v>0.016064</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>372</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.016482</v>
+        <v>0.016479</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>373</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.017063</v>
+        <v>0.017049</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>374</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.017097</v>
+        <v>0.017071</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>375</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.017151</v>
+        <v>0.017233</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>376</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.017156</v>
+        <v>0.01724</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>377</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.017482</v>
+        <v>0.017276</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>378</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.017533</v>
+        <v>0.017563</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>379</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.018054</v>
+        <v>0.01788</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>380</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.018311</v>
+        <v>0.018426</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>381</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.018438</v>
+        <v>0.018571</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>382</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.019053</v>
+        <v>0.019116</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>383</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.019121</v>
+        <v>0.019176</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>384</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.019252</v>
+        <v>0.01921</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>385</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.019362</v>
+        <v>0.019326</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>386</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.019387</v>
+        <v>0.019496</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>387</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.019478</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>388</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.020561</v>
+        <v>0.020373</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>389</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.020755</v>
+        <v>0.020797</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>390</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.021092</v>
+        <v>0.021156</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>391</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.021536</v>
+        <v>0.021443</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>392</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.02172</v>
+        <v>0.021895</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>393</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.022173</v>
+        <v>0.022266</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>394</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.022371</v>
+        <v>0.022271</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>395</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.02338</v>
+        <v>0.022904</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>396</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.023403</v>
+        <v>0.023535</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>397</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.023862</v>
+        <v>0.023719</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>398</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.024222</v>
+        <v>0.024212</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>399</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.024862</v>
+        <v>0.024754</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>400</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.025123</v>
+        <v>0.025019</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>401</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.025125</v>
+        <v>0.02503</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>402</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.025128</v>
+        <v>0.025078</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>403</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.025317</v>
+        <v>0.02532</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>404</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.025363</v>
+        <v>0.025364</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>405</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.02567</v>
+        <v>0.025404</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>406</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.025842</v>
+        <v>0.025574</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>407</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.02588</v>
+        <v>0.025879</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>408</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.026926</v>
+        <v>0.026372</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>409</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.027141</v>
+        <v>0.026642</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>410</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.027503</v>
+        <v>0.02728</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>411</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.027642</v>
+        <v>0.027742</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>412</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.027917</v>
+        <v>0.027802</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>413</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.027991</v>
+        <v>0.028106</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>414</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.028249</v>
+        <v>0.028315</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>415</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.028486</v>
+        <v>0.028721</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>416</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.028603</v>
+        <v>0.02879</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>417</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.028868</v>
+        <v>0.028918</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>418</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.028891</v>
+        <v>0.02914</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>419</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.029493</v>
+        <v>0.029677</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>420</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.029576</v>
+        <v>0.029706</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>421</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.029871</v>
+        <v>0.029846</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>422</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.029943</v>
+        <v>0.029887</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>423</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.030038</v>
+        <v>0.029906</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>424</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.030078</v>
+        <v>0.029931</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>425</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.030154</v>
+        <v>0.029984</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>426</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.030558</v>
+        <v>0.030831</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>427</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.031231</v>
+        <v>0.031302</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>428</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.031258</v>
+        <v>0.031426</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>429</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.031993</v>
+        <v>0.031596</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>430</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.032085</v>
+        <v>0.032234</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>431</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.032133</v>
+        <v>0.032305</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>432</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.032733</v>
+        <v>0.032685</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>433</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.033574</v>
+        <v>0.033244</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>434</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.03376</v>
+        <v>0.033423</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>435</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.03386</v>
+        <v>0.033742</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>436</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.03392</v>
+        <v>0.033854</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>437</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.033963</v>
+        <v>0.03395</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>438</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.034112</v>
+        <v>0.034049</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>439</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.034614</v>
+        <v>0.034706</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>440</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.034674</v>
+        <v>0.034758</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>441</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.034699</v>
+        <v>0.03477</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>442</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.03487</v>
+        <v>0.034993</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>443</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.035083</v>
+        <v>0.035062</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>444</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.035377</v>
+        <v>0.035343</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>445</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.0354</v>
+        <v>0.035495</v>
       </c>
     </row>
     <row r="1122">
@@ -15016,7 +15016,7 @@
         <v>447</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.036284</v>
+        <v>0.036041</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>448</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.037507</v>
+        <v>0.037335</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>449</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.037653</v>
+        <v>0.037822</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>450</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.037745</v>
+        <v>0.038043</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>451</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.038517</v>
+        <v>0.038277</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>452</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.038555</v>
+        <v>0.038545</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>453</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.038556</v>
+        <v>0.038808</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>454</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.039037</v>
+        <v>0.038859</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>455</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.039205</v>
+        <v>0.039551</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>456</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.039382</v>
+        <v>0.039641</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>457</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.039644</v>
+        <v>0.039785</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>458</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.039784</v>
+        <v>0.039882</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>459</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.040018</v>
+        <v>0.040194</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>460</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.040251</v>
+        <v>0.040208</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>461</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.040529</v>
+        <v>0.040846</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>462</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.04167</v>
+        <v>0.041278</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>463</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.041827</v>
+        <v>0.041661</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>464</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.042015</v>
+        <v>0.042152</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>465</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.042187</v>
+        <v>0.042256</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>466</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.042475</v>
+        <v>0.04254</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>467</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.04255</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>468</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.042673</v>
+        <v>0.042916</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>469</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.042967</v>
+        <v>0.043004</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>470</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.042974</v>
+        <v>0.043112</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>471</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.043181</v>
+        <v>0.04329</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>472</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.043192</v>
+        <v>0.043477</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>473</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.043392</v>
+        <v>0.043583</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>474</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.043414</v>
+        <v>0.043643</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>475</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.04374</v>
+        <v>0.043733</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>476</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.043888</v>
+        <v>0.044173</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>477</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.044514</v>
+        <v>0.044677</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>478</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.044625</v>
+        <v>0.044806</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>479</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.044781</v>
+        <v>0.044819</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>480</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.045068</v>
+        <v>0.044895</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>481</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.045227</v>
+        <v>0.044901</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>482</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.04539</v>
+        <v>0.045545</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>483</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.045593</v>
+        <v>0.04585</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>484</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.04626</v>
+        <v>0.046267</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>485</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.046845</v>
+        <v>0.046363</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>486</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.047096</v>
+        <v>0.046497</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>487</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.047595</v>
+        <v>0.047747</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>488</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.047765</v>
+        <v>0.047979</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>489</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.048177</v>
+        <v>0.048217</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>490</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.04899</v>
+        <v>0.048277</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>491</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.049385</v>
+        <v>0.049311</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>492</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.049416</v>
+        <v>0.049479</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>493</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.049541</v>
+        <v>0.049815</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>494</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.050824</v>
+        <v>0.05042</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>495</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.051619</v>
+        <v>0.050841</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>496</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.051942</v>
+        <v>0.052325</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>497</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.052547</v>
+        <v>0.052868</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>498</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.053066</v>
+        <v>0.053207</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>499</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.053281</v>
+        <v>0.053393</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>500</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.053663</v>
+        <v>0.053528</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>501</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.053931</v>
+        <v>0.053602</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>502</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.054494</v>
+        <v>0.053864</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>503</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.054545</v>
+        <v>0.054203</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>504</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.055198</v>
+        <v>0.054594</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>505</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.055231</v>
+        <v>0.055216</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>506</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.05541</v>
+        <v>0.055266</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>507</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.055463</v>
+        <v>0.055299</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>508</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.055584</v>
+        <v>0.055563</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>509</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.055621</v>
+        <v>0.055912</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>510</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.055839</v>
+        <v>0.056087</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>511</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.057096</v>
+        <v>0.05698</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>512</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.057478</v>
+        <v>0.05758</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>513</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.057876</v>
+        <v>0.057897</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>514</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.058496</v>
+        <v>0.058081</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>515</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.059825</v>
+        <v>0.059321</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>516</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.059871</v>
+        <v>0.059863</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>517</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.059884</v>
+        <v>0.05987</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>518</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.060254</v>
+        <v>0.060205</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>519</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.060748</v>
+        <v>0.060766</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>520</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.061163</v>
+        <v>0.061329</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>521</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.061501</v>
+        <v>0.061413</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>522</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.061709</v>
+        <v>0.061913</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>523</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.062537</v>
+        <v>0.062426</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>524</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.063568</v>
+        <v>0.063253</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>525</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.06386500000000001</v>
+        <v>0.064389</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>526</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.065997</v>
+        <v>0.06528399999999999</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>527</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.066236</v>
+        <v>0.066112</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>528</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.066733</v>
+        <v>0.066692</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>529</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.066843</v>
+        <v>0.066969</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>530</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.066885</v>
+        <v>0.067117</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>531</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.067568</v>
+        <v>0.067134</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>532</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.067622</v>
+        <v>0.06777</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>533</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.06771000000000001</v>
+        <v>0.067789</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>534</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.06807199999999999</v>
+        <v>0.068091</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>535</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.068519</v>
+        <v>0.068092</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>536</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.06897200000000001</v>
+        <v>0.06845999999999999</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>537</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.069174</v>
+        <v>0.068522</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>538</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.069176</v>
+        <v>0.068814</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>539</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.06956</v>
+        <v>0.06907099999999999</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>540</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.06965200000000001</v>
+        <v>0.069317</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>541</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.06968000000000001</v>
+        <v>0.069463</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>542</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.070913</v>
+        <v>0.071409</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>543</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.071634</v>
+        <v>0.072283</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>544</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.07173499999999999</v>
+        <v>0.072382</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>545</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.072724</v>
+        <v>0.072753</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>546</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.073514</v>
+        <v>0.073181</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>547</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.07398100000000001</v>
+        <v>0.07374699999999999</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>548</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.07413500000000001</v>
+        <v>0.074073</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>549</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.07430200000000001</v>
+        <v>0.07409399999999999</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>550</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.074549</v>
+        <v>0.07437299999999999</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>551</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.074602</v>
+        <v>0.074558</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>552</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.075512</v>
+        <v>0.075156</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>553</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.075693</v>
+        <v>0.075652</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>554</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.075881</v>
+        <v>0.076223</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>555</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.07727100000000001</v>
+        <v>0.076545</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>556</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.077406</v>
+        <v>0.076932</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>557</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.077641</v>
+        <v>0.077782</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>558</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.077734</v>
+        <v>0.07785599999999999</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>559</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.078125</v>
+        <v>0.077919</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>560</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.078233</v>
+        <v>0.078192</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>561</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.078558</v>
+        <v>0.07871599999999999</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>562</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.078664</v>
+        <v>0.078904</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>563</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.07870199999999999</v>
+        <v>0.07910399999999999</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>564</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.079123</v>
+        <v>0.07917</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>565</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.080346</v>
+        <v>0.080233</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>566</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.083567</v>
+        <v>0.083747</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>567</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.083783</v>
+        <v>0.084022</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>568</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.084368</v>
+        <v>0.084894</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>569</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.085267</v>
+        <v>0.084939</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>570</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.085907</v>
+        <v>0.08558399999999999</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>571</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.086119</v>
+        <v>0.086018</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>572</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.087307</v>
+        <v>0.08688800000000001</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>573</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.08731700000000001</v>
+        <v>0.087052</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>574</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.087342</v>
+        <v>0.087921</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>575</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.088059</v>
+        <v>0.088004</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>576</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.08874899999999999</v>
+        <v>0.088063</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>577</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.089513</v>
+        <v>0.08876100000000001</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>578</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.089728</v>
+        <v>0.089491</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>579</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.090035</v>
+        <v>0.089549</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>580</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.090933</v>
+        <v>0.090027</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>581</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.09107</v>
+        <v>0.09027499999999999</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>582</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.091888</v>
+        <v>0.091874</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>583</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.092057</v>
+        <v>0.092524</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>584</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.092192</v>
+        <v>0.092546</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>585</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.092596</v>
+        <v>0.092748</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>586</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.093151</v>
+        <v>0.093891</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>587</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.093668</v>
+        <v>0.09418600000000001</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>588</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.097619</v>
+        <v>0.098229</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>589</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.09816900000000001</v>
+        <v>0.098398</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>590</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.09941700000000001</v>
+        <v>0.098486</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>591</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.099678</v>
+        <v>0.09854499999999999</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>592</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.099971</v>
+        <v>0.09925100000000001</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>593</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.100061</v>
+        <v>0.100148</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>594</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.100268</v>
+        <v>0.100708</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>595</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.100625</v>
+        <v>0.100955</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>596</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.101773</v>
+        <v>0.101141</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>597</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.101871</v>
+        <v>0.101172</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>598</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.101972</v>
+        <v>0.101465</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>599</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.102054</v>
+        <v>0.101628</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>600</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.103475</v>
+        <v>0.102175</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>601</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.104028</v>
+        <v>0.103661</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>602</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.104299</v>
+        <v>0.104685</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>603</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.105687</v>
+        <v>0.105134</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>604</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.107026</v>
+        <v>0.107492</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>605</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.108516</v>
+        <v>0.108731</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>606</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.110065</v>
+        <v>0.109892</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>607</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.110445</v>
+        <v>0.110249</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>608</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.110998</v>
+        <v>0.111221</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>609</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.111408</v>
+        <v>0.111884</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>610</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.112827</v>
+        <v>0.112312</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>611</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.11441</v>
+        <v>0.115447</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>612</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.119253</v>
+        <v>0.118503</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>613</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.119685</v>
+        <v>0.120042</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>614</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.120444</v>
+        <v>0.120274</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>615</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.121304</v>
+        <v>0.121653</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>616</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.123874</v>
+        <v>0.122844</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>617</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.125588</v>
+        <v>0.124478</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>618</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.125807</v>
+        <v>0.125298</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>619</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.1275</v>
+        <v>0.126769</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>620</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.128215</v>
+        <v>0.127751</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>621</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.129437</v>
+        <v>0.129674</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>622</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.129977</v>
+        <v>0.130566</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>623</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.130363</v>
+        <v>0.130831</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>624</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.130479</v>
+        <v>0.131416</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>625</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.131886</v>
+        <v>0.132641</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>626</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.131936</v>
+        <v>0.132662</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>627</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.133107</v>
+        <v>0.13297</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>628</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.135963</v>
+        <v>0.134626</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>629</v>
       </c>
       <c r="C1305" t="n">
-        <v>0.137372</v>
+        <v>0.134864</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>630</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.138164</v>
+        <v>0.136036</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>631</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.138343</v>
+        <v>0.138023</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>632</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.138419</v>
+        <v>0.139471</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>633</v>
       </c>
       <c r="C1309" t="n">
-        <v>0.13867</v>
+        <v>0.139928</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>634</v>
       </c>
       <c r="C1310" t="n">
-        <v>0.14116</v>
+        <v>0.141362</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>635</v>
       </c>
       <c r="C1311" t="n">
-        <v>0.1414</v>
+        <v>0.141618</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>636</v>
       </c>
       <c r="C1312" t="n">
-        <v>0.142461</v>
+        <v>0.141784</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>637</v>
       </c>
       <c r="C1313" t="n">
-        <v>0.143079</v>
+        <v>0.142535</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>638</v>
       </c>
       <c r="C1314" t="n">
-        <v>0.144764</v>
+        <v>0.143625</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>639</v>
       </c>
       <c r="C1315" t="n">
-        <v>0.145934</v>
+        <v>0.144243</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>640</v>
       </c>
       <c r="C1316" t="n">
-        <v>0.153384</v>
+        <v>0.153464</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>641</v>
       </c>
       <c r="C1317" t="n">
-        <v>0.154815</v>
+        <v>0.154536</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>642</v>
       </c>
       <c r="C1318" t="n">
-        <v>0.154891</v>
+        <v>0.155832</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>643</v>
       </c>
       <c r="C1319" t="n">
-        <v>0.159054</v>
+        <v>0.15842</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>644</v>
       </c>
       <c r="C1320" t="n">
-        <v>0.162137</v>
+        <v>0.161951</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>645</v>
       </c>
       <c r="C1321" t="n">
-        <v>0.162906</v>
+        <v>0.164151</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>646</v>
       </c>
       <c r="C1322" t="n">
-        <v>0.165839</v>
+        <v>0.16442</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>647</v>
       </c>
       <c r="C1323" t="n">
-        <v>0.169061</v>
+        <v>0.169395</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>648</v>
       </c>
       <c r="C1324" t="n">
-        <v>0.170113</v>
+        <v>0.171096</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>649</v>
       </c>
       <c r="C1325" t="n">
-        <v>0.177933</v>
+        <v>0.178615</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>650</v>
       </c>
       <c r="C1326" t="n">
-        <v>0.178189</v>
+        <v>0.179498</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>651</v>
       </c>
       <c r="C1327" t="n">
-        <v>0.179015</v>
+        <v>0.179697</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>652</v>
       </c>
       <c r="C1328" t="n">
-        <v>0.180992</v>
+        <v>0.182582</v>
       </c>
     </row>
     <row r="1329">
@@ -17694,7 +17694,7 @@
         <v>653</v>
       </c>
       <c r="C1329" t="n">
-        <v>0.183889</v>
+        <v>0.184452</v>
       </c>
     </row>
     <row r="1330">
@@ -17707,7 +17707,7 @@
         <v>654</v>
       </c>
       <c r="C1330" t="n">
-        <v>0.185548</v>
+        <v>0.185465</v>
       </c>
     </row>
     <row r="1331">
@@ -17720,7 +17720,7 @@
         <v>655</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.186009</v>
+        <v>0.187602</v>
       </c>
     </row>
     <row r="1332">
@@ -17733,7 +17733,7 @@
         <v>656</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.195397</v>
+        <v>0.194423</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>657</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.196313</v>
+        <v>0.197149</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>658</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.200034</v>
+        <v>0.197429</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>659</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.208874</v>
+        <v>0.208681</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>660</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.208976</v>
+        <v>0.210734</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>661</v>
       </c>
       <c r="C1337" t="n">
-        <v>0.214644</v>
+        <v>0.210786</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>662</v>
       </c>
       <c r="C1338" t="n">
-        <v>0.228307</v>
+        <v>0.228963</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>663</v>
       </c>
       <c r="C1339" t="n">
-        <v>0.232818</v>
+        <v>0.23467</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>664</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.241414</v>
+        <v>0.243604</v>
       </c>
     </row>
     <row r="1341">
@@ -17850,7 +17850,7 @@
         <v>665</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.241966</v>
+        <v>0.24397</v>
       </c>
     </row>
     <row r="1342">
@@ -17863,7 +17863,7 @@
         <v>666</v>
       </c>
       <c r="C1342" t="n">
-        <v>0.244353</v>
+        <v>0.246569</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>667</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>668</v>
       </c>
       <c r="C1344" t="n">
-        <v>0.262818</v>
+        <v>0.264682</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>669</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.271117</v>
+        <v>0.272675</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>670</v>
       </c>
       <c r="C1346" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>671</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.30904</v>
+        <v>0.311792</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>672</v>
       </c>
       <c r="C1348" t="n">
-        <v>0.33963</v>
+        <v>0.34116</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>673</v>
       </c>
       <c r="C1349" t="n">
-        <v>0.483999</v>
+        <v>0.487269</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -1067,7 +1067,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.08276</v>
+        <v>-0.082706</v>
       </c>
     </row>
     <row r="51">
@@ -8880,7 +8880,7 @@
         <v>0</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.271939</v>
+        <v>-0.271962</v>
       </c>
     </row>
     <row r="652">
@@ -8893,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.241487</v>
+        <v>-0.241418</v>
       </c>
     </row>
     <row r="653">
@@ -8906,7 +8906,7 @@
         <v>2</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.17094</v>
+        <v>-0.171002</v>
       </c>
     </row>
     <row r="654">
@@ -8919,7 +8919,7 @@
         <v>3</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.143307</v>
+        <v>-0.143277</v>
       </c>
     </row>
     <row r="655">
@@ -8932,7 +8932,7 @@
         <v>4</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.123235</v>
+        <v>-0.1232</v>
       </c>
     </row>
     <row r="656">
@@ -8945,7 +8945,7 @@
         <v>5</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.121746</v>
+        <v>-0.121829</v>
       </c>
     </row>
     <row r="657">
@@ -8958,7 +8958,7 @@
         <v>6</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.120731</v>
+        <v>-0.121092</v>
       </c>
     </row>
     <row r="658">
@@ -8971,7 +8971,7 @@
         <v>7</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.117126</v>
+        <v>-0.117243</v>
       </c>
     </row>
     <row r="659">
@@ -8984,7 +8984,7 @@
         <v>8</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.112633</v>
+        <v>-0.112613</v>
       </c>
     </row>
     <row r="660">
@@ -8997,7 +8997,7 @@
         <v>9</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.112198</v>
+        <v>-0.112227</v>
       </c>
     </row>
     <row r="661">
@@ -9010,7 +9010,7 @@
         <v>10</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.109586</v>
+        <v>-0.109844</v>
       </c>
     </row>
     <row r="662">
@@ -9023,7 +9023,7 @@
         <v>11</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.106655</v>
+        <v>-0.106918</v>
       </c>
     </row>
     <row r="663">
@@ -9036,7 +9036,7 @@
         <v>12</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.106575</v>
+        <v>-0.106631</v>
       </c>
     </row>
     <row r="664">
@@ -9049,7 +9049,7 @@
         <v>13</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.106051</v>
+        <v>-0.106088</v>
       </c>
     </row>
     <row r="665">
@@ -9062,7 +9062,7 @@
         <v>14</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.104398</v>
+        <v>-0.104397</v>
       </c>
     </row>
     <row r="666">
@@ -9075,7 +9075,7 @@
         <v>15</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.104275</v>
+        <v>-0.104303</v>
       </c>
     </row>
     <row r="667">
@@ -9088,7 +9088,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.102735</v>
+        <v>-0.102784</v>
       </c>
     </row>
     <row r="668">
@@ -9101,7 +9101,7 @@
         <v>17</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.098649</v>
+        <v>-0.09882299999999999</v>
       </c>
     </row>
     <row r="669">
@@ -9114,7 +9114,7 @@
         <v>18</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.09833699999999999</v>
+        <v>-0.09843</v>
       </c>
     </row>
     <row r="670">
@@ -9127,7 +9127,7 @@
         <v>19</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.096731</v>
+        <v>-0.09675499999999999</v>
       </c>
     </row>
     <row r="671">
@@ -9140,7 +9140,7 @@
         <v>20</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.096149</v>
+        <v>-0.09612900000000001</v>
       </c>
     </row>
     <row r="672">
@@ -9153,7 +9153,7 @@
         <v>21</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.09518799999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
     </row>
     <row r="673">
@@ -9166,7 +9166,7 @@
         <v>22</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.095114</v>
+        <v>-0.095182</v>
       </c>
     </row>
     <row r="674">
@@ -9179,7 +9179,7 @@
         <v>23</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.09472800000000001</v>
+        <v>-0.094872</v>
       </c>
     </row>
     <row r="675">
@@ -9192,7 +9192,7 @@
         <v>24</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.094247</v>
+        <v>-0.094221</v>
       </c>
     </row>
     <row r="676">
@@ -9205,7 +9205,7 @@
         <v>25</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.091741</v>
+        <v>-0.091893</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.091269</v>
+        <v>-0.09132999999999999</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>27</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.090548</v>
+        <v>-0.090612</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>28</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.090222</v>
+        <v>-0.090227</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>29</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.08980299999999999</v>
+        <v>-0.089808</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>30</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.086798</v>
+        <v>-0.086864</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>31</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.086449</v>
+        <v>-0.08650099999999999</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>32</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.084728</v>
+        <v>-0.084914</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>33</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.08434999999999999</v>
+        <v>-0.084409</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>34</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.08308500000000001</v>
+        <v>-0.08314199999999999</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>35</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.07979899999999999</v>
+        <v>-0.079776</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>36</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.079289</v>
+        <v>-0.079272</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>37</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.078696</v>
+        <v>-0.07868600000000001</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>38</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.07734199999999999</v>
+        <v>-0.07732600000000001</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>39</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.07564800000000001</v>
+        <v>-0.07563400000000001</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>40</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.073591</v>
+        <v>-0.07366200000000001</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>41</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.07267800000000001</v>
+        <v>-0.072695</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>42</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.071934</v>
+        <v>-0.071973</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>43</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.070175</v>
+        <v>-0.070157</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>44</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.069781</v>
+        <v>-0.0698</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>45</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.068899</v>
+        <v>-0.068885</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>46</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.06786</v>
+        <v>-0.06786499999999999</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>47</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.06768200000000001</v>
+        <v>-0.067706</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>48</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.067552</v>
+        <v>-0.067617</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>49</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.06730999999999999</v>
+        <v>-0.067358</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>50</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.066154</v>
+        <v>-0.066195</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>51</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.065397</v>
+        <v>-0.065402</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>52</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.064738</v>
+        <v>-0.064723</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>53</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.064357</v>
+        <v>-0.064377</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>54</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.063586</v>
+        <v>-0.063752</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>55</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.063568</v>
+        <v>-0.063565</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>56</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.063093</v>
+        <v>-0.06308</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>57</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.062351</v>
+        <v>-0.06236</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>58</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.062033</v>
+        <v>-0.062095</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>59</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.061946</v>
+        <v>-0.061933</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>60</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.061079</v>
+        <v>-0.061084</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>61</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.060501</v>
+        <v>-0.060496</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>62</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.060349</v>
+        <v>-0.060392</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>63</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.060301</v>
+        <v>-0.060335</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>64</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.059896</v>
+        <v>-0.059887</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>65</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.059391</v>
+        <v>-0.059337</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>66</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.058443</v>
+        <v>-0.058517</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>67</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.057552</v>
+        <v>-0.057607</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>68</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.056346</v>
+        <v>-0.056369</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>69</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.055509</v>
+        <v>-0.055569</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>70</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.054982</v>
+        <v>-0.054979</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>71</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.054804</v>
+        <v>-0.054788</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>72</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.054692</v>
+        <v>-0.054701</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>73</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.05463</v>
+        <v>-0.054616</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>74</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.053561</v>
+        <v>-0.053546</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>75</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.053178</v>
+        <v>-0.053177</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>76</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.053085</v>
+        <v>-0.053101</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>77</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.052806</v>
+        <v>-0.052837</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>78</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.052748</v>
+        <v>-0.052732</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>79</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.051828</v>
+        <v>-0.051823</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>80</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.051557</v>
+        <v>-0.051607</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>81</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.05135</v>
+        <v>-0.051385</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>82</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.051341</v>
+        <v>-0.05134</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>83</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.05133</v>
+        <v>-0.051316</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>84</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.051266</v>
+        <v>-0.051273</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>85</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.050905</v>
+        <v>-0.050934</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>86</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.050643</v>
+        <v>-0.050632</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>87</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.04994</v>
+        <v>-0.050043</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>88</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.049527</v>
+        <v>-0.049552</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>89</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.049455</v>
+        <v>-0.04955</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>90</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.049439</v>
+        <v>-0.049442</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>91</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.048537</v>
+        <v>-0.048619</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>92</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.048441</v>
+        <v>-0.048459</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>93</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.048387</v>
+        <v>-0.048432</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>94</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.048185</v>
+        <v>-0.048171</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>95</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.047475</v>
+        <v>-0.047462</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>96</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.046871</v>
+        <v>-0.046858</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>97</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.046799</v>
+        <v>-0.046788</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>98</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.046379</v>
+        <v>-0.046417</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>99</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.046148</v>
+        <v>-0.046288</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>100</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.046131</v>
+        <v>-0.046205</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>101</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.045657</v>
+        <v>-0.045673</v>
       </c>
     </row>
     <row r="753">
@@ -10219,7 +10219,7 @@
         <v>103</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.045368</v>
+        <v>-0.045379</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>104</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.044851</v>
+        <v>-0.044856</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>105</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.044432</v>
+        <v>-0.044458</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>106</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.044393</v>
+        <v>-0.044397</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>107</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.044355</v>
+        <v>-0.04438</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>108</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.044177</v>
+        <v>-0.044165</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>109</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.04405</v>
+        <v>-0.044055</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>110</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.042023</v>
+        <v>-0.042034</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>111</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.04038</v>
+        <v>-0.040427</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>112</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.04008</v>
+        <v>-0.040075</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>113</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.039963</v>
+        <v>-0.039964</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>114</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.038691</v>
+        <v>-0.038716</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>115</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.037984</v>
+        <v>-0.038</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>116</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.037914</v>
+        <v>-0.037906</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>117</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.037862</v>
+        <v>-0.037903</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>118</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.037196</v>
+        <v>-0.037186</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>119</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.036582</v>
+        <v>-0.036609</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>120</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.036129</v>
+        <v>-0.03612</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>121</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.035928</v>
+        <v>-0.035949</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>122</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.035883</v>
+        <v>-0.035882</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>123</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.035232</v>
+        <v>-0.035225</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>124</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.034011</v>
+        <v>-0.034002</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>125</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.033892</v>
+        <v>-0.033912</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>126</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.033527</v>
+        <v>-0.033554</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>127</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.033392</v>
+        <v>-0.033411</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>128</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.032743</v>
+        <v>-0.032734</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>129</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.032399</v>
+        <v>-0.032434</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>130</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.032016</v>
+        <v>-0.032013</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>131</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.031713</v>
+        <v>-0.031777</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>132</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.031623</v>
+        <v>-0.031614</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>133</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.030681</v>
+        <v>-0.030766</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>134</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.03031</v>
+        <v>-0.030311</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>135</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.02996</v>
+        <v>-0.029957</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>136</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.029952</v>
+        <v>-0.029948</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>137</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.029323</v>
+        <v>-0.029317</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>138</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.028867</v>
+        <v>-0.028861</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>139</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.028693</v>
+        <v>-0.028687</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>140</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.028238</v>
+        <v>-0.028273</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>141</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.028229</v>
+        <v>-0.028248</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>142</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.028199</v>
+        <v>-0.028209</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>143</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.02819</v>
+        <v>-0.028196</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>144</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.027523</v>
+        <v>-0.02752</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>145</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.027384</v>
+        <v>-0.02738</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>146</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.026807</v>
+        <v>-0.026845</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>147</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.026251</v>
+        <v>-0.026252</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>148</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.025522</v>
+        <v>-0.025537</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>149</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.02526</v>
+        <v>-0.025255</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>150</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.02506</v>
+        <v>-0.025071</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>151</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.024147</v>
+        <v>-0.024148</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>152</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.024115</v>
+        <v>-0.024141</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>153</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.02385</v>
+        <v>-0.023844</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>154</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.02358</v>
+        <v>-0.023573</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>155</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.023465</v>
+        <v>-0.023458</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>156</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.022216</v>
+        <v>-0.022265</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>157</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.02199</v>
+        <v>-0.021994</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>158</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.021924</v>
+        <v>-0.021919</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>159</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.021643</v>
+        <v>-0.021637</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>160</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.021479</v>
+        <v>-0.021478</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>161</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.021137</v>
+        <v>-0.021167</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>162</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.020914</v>
+        <v>-0.020927</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>163</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.020283</v>
+        <v>-0.020319</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>164</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.020218</v>
+        <v>-0.02022</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>165</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.019983</v>
+        <v>-0.019991</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>166</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.019922</v>
+        <v>-0.019965</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>167</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.019449</v>
+        <v>-0.019452</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>168</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.019275</v>
+        <v>-0.019269</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>169</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.019188</v>
+        <v>-0.019187</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>170</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.01915</v>
+        <v>-0.019144</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>171</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.018885</v>
+        <v>-0.018891</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>172</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.018793</v>
+        <v>-0.018795</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>173</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.018509</v>
+        <v>-0.018535</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>174</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.018263</v>
+        <v>-0.018258</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>175</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.017963</v>
+        <v>-0.017989</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>176</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.017913</v>
+        <v>-0.017909</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>177</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.017865</v>
+        <v>-0.017876</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>178</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.017253</v>
+        <v>-0.017256</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>179</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.017253</v>
+        <v>-0.017248</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>180</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.016982</v>
+        <v>-0.016985</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>181</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.016659</v>
+        <v>-0.016655</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>182</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.015992</v>
+        <v>-0.015994</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>183</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.015016</v>
+        <v>-0.015022</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>184</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.014742</v>
+        <v>-0.01475</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>185</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.014549</v>
+        <v>-0.014553</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>186</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.013772</v>
+        <v>-0.013768</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>187</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.013672</v>
+        <v>-0.013668</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>188</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.013287</v>
+        <v>-0.01329</v>
       </c>
     </row>
     <row r="840">
@@ -11350,7 +11350,7 @@
         <v>190</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.013065</v>
+        <v>-0.013085</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>191</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.012515</v>
+        <v>-0.012512</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>192</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.012434</v>
+        <v>-0.012435</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>193</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.012329</v>
+        <v>-0.012365</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>194</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.012182</v>
+        <v>-0.01218</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>195</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.011965</v>
+        <v>-0.011962</v>
       </c>
     </row>
     <row r="847">
@@ -11441,7 +11441,7 @@
         <v>197</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.011538</v>
+        <v>-0.011551</v>
       </c>
     </row>
     <row r="849">
@@ -11467,7 +11467,7 @@
         <v>199</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.010853</v>
+        <v>-0.010852</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>200</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.010524</v>
+        <v>-0.010521</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>201</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.009752</v>
+        <v>-0.009763000000000001</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>202</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.009502999999999999</v>
+        <v>-0.009521</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>203</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.009367</v>
+        <v>-0.009386</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>204</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.009105</v>
+        <v>-0.009103</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>205</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.00906</v>
+        <v>-0.009057000000000001</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>206</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.008869</v>
+        <v>-0.008876999999999999</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>207</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.008843</v>
+        <v>-0.008841</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>208</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.008784999999999999</v>
+        <v>-0.008794</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>209</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.007842</v>
+        <v>-0.007841000000000001</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>210</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.007806</v>
+        <v>-0.007805</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>211</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.007409</v>
+        <v>-0.007407</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>212</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.007372</v>
+        <v>-0.007374</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>213</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.007111</v>
+        <v>-0.007109</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>214</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.007015</v>
+        <v>-0.007013</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>215</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.006906</v>
+        <v>-0.006904</v>
       </c>
     </row>
     <row r="867">
@@ -11701,7 +11701,7 @@
         <v>217</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.00634</v>
+        <v>-0.006347</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>218</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.005951</v>
+        <v>-0.005966</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>219</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.005644</v>
+        <v>-0.005648</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>220</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.005639</v>
+        <v>-0.005638</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>221</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.005596</v>
+        <v>-0.005595</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>222</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.005321</v>
+        <v>-0.005325</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>223</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.00477</v>
+        <v>-0.004769</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>224</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.004676</v>
+        <v>-0.004675</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>225</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.004538</v>
+        <v>-0.004536</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>226</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.00426</v>
+        <v>-0.004259</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>227</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.004218</v>
+        <v>-0.004217</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>228</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.004207</v>
+        <v>-0.00421</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>229</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.004178</v>
+        <v>-0.004176</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>230</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.004069</v>
+        <v>-0.004068</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>231</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.003769</v>
+        <v>-0.003771</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>232</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.003264</v>
+        <v>-0.003263</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>233</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.003247</v>
+        <v>-0.00325</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>234</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.00305</v>
+        <v>-0.003052</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>235</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.002777</v>
+        <v>-0.002784</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>236</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.002722</v>
+        <v>-0.002724</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>237</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.002501</v>
+        <v>-0.002502</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>238</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.002187</v>
+        <v>-0.002195</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>239</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.002101</v>
+        <v>-0.002103</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>240</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.001715</v>
+        <v>-0.001718</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>241</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.001683</v>
+        <v>-0.001685</v>
       </c>
     </row>
     <row r="893">
@@ -12039,7 +12039,7 @@
         <v>243</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.001552</v>
+        <v>-0.001556</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>244</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.001362</v>
+        <v>-0.001366</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>245</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.001201</v>
+        <v>-0.0012</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>246</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.0006489999999999999</v>
+        <v>-0.000648</v>
       </c>
     </row>
     <row r="898">
@@ -12208,7 +12208,7 @@
         <v>256</v>
       </c>
       <c r="C907" t="n">
-        <v>0.001846</v>
+        <v>0.001845</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>257</v>
       </c>
       <c r="C908" t="n">
-        <v>0.002018</v>
+        <v>0.00202</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>258</v>
       </c>
       <c r="C909" t="n">
-        <v>0.002228</v>
+        <v>0.002227</v>
       </c>
     </row>
     <row r="910">
@@ -12260,7 +12260,7 @@
         <v>260</v>
       </c>
       <c r="C911" t="n">
-        <v>0.002517</v>
+        <v>0.002518</v>
       </c>
     </row>
     <row r="912">
@@ -12286,7 +12286,7 @@
         <v>262</v>
       </c>
       <c r="C913" t="n">
-        <v>0.002745</v>
+        <v>0.002749</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>263</v>
       </c>
       <c r="C914" t="n">
-        <v>0.002889</v>
+        <v>0.002894</v>
       </c>
     </row>
     <row r="915">
@@ -12325,7 +12325,7 @@
         <v>265</v>
       </c>
       <c r="C916" t="n">
-        <v>0.003345</v>
+        <v>0.003346</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>266</v>
       </c>
       <c r="C917" t="n">
-        <v>0.003468</v>
+        <v>0.003467</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>267</v>
       </c>
       <c r="C918" t="n">
-        <v>0.003888</v>
+        <v>0.00389</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>268</v>
       </c>
       <c r="C919" t="n">
-        <v>0.004531</v>
+        <v>0.00453</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>269</v>
       </c>
       <c r="C920" t="n">
-        <v>0.004608</v>
+        <v>0.004607</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>270</v>
       </c>
       <c r="C921" t="n">
-        <v>0.004828</v>
+        <v>0.004829</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>271</v>
       </c>
       <c r="C922" t="n">
-        <v>0.005</v>
+        <v>0.005012</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>272</v>
       </c>
       <c r="C923" t="n">
-        <v>0.005102</v>
+        <v>0.005101</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>273</v>
       </c>
       <c r="C924" t="n">
-        <v>0.005116</v>
+        <v>0.005123</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>274</v>
       </c>
       <c r="C925" t="n">
-        <v>0.005235</v>
+        <v>0.005234</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>275</v>
       </c>
       <c r="C926" t="n">
-        <v>0.005542</v>
+        <v>0.005545</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>276</v>
       </c>
       <c r="C927" t="n">
-        <v>0.005577</v>
+        <v>0.005587</v>
       </c>
     </row>
     <row r="928">
@@ -12494,7 +12494,7 @@
         <v>278</v>
       </c>
       <c r="C929" t="n">
-        <v>0.005807</v>
+        <v>0.005805</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>279</v>
       </c>
       <c r="C930" t="n">
-        <v>0.005978</v>
+        <v>0.005982</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>280</v>
       </c>
       <c r="C931" t="n">
-        <v>0.005983</v>
+        <v>0.005989</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>281</v>
       </c>
       <c r="C932" t="n">
-        <v>0.006566</v>
+        <v>0.006564</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>282</v>
       </c>
       <c r="C933" t="n">
-        <v>0.006866</v>
+        <v>0.006864</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>283</v>
       </c>
       <c r="C934" t="n">
-        <v>0.007427</v>
+        <v>0.007425</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>284</v>
       </c>
       <c r="C935" t="n">
-        <v>0.008344000000000001</v>
+        <v>0.008342</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>285</v>
       </c>
       <c r="C936" t="n">
-        <v>0.008581999999999999</v>
+        <v>0.008597</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>286</v>
       </c>
       <c r="C937" t="n">
-        <v>0.008765999999999999</v>
+        <v>0.008770999999999999</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>287</v>
       </c>
       <c r="C938" t="n">
-        <v>0.008921</v>
+        <v>0.00894</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>288</v>
       </c>
       <c r="C939" t="n">
-        <v>0.008945</v>
+        <v>0.008942</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>289</v>
       </c>
       <c r="C940" t="n">
-        <v>0.009116000000000001</v>
+        <v>0.00912</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>290</v>
       </c>
       <c r="C941" t="n">
-        <v>0.009168000000000001</v>
+        <v>0.009166000000000001</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>291</v>
       </c>
       <c r="C942" t="n">
-        <v>0.009209</v>
+        <v>0.009220000000000001</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>292</v>
       </c>
       <c r="C943" t="n">
-        <v>0.009480000000000001</v>
+        <v>0.009479</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>293</v>
       </c>
       <c r="C944" t="n">
-        <v>0.009611</v>
+        <v>0.009617000000000001</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>294</v>
       </c>
       <c r="C945" t="n">
-        <v>0.009792</v>
+        <v>0.009793</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>295</v>
       </c>
       <c r="C946" t="n">
-        <v>0.009988</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>296</v>
       </c>
       <c r="C947" t="n">
-        <v>0.010736</v>
+        <v>0.01076</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>297</v>
       </c>
       <c r="C948" t="n">
-        <v>0.010855</v>
+        <v>0.010857</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>298</v>
       </c>
       <c r="C949" t="n">
-        <v>0.010898</v>
+        <v>0.010896</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>299</v>
       </c>
       <c r="C950" t="n">
-        <v>0.01109</v>
+        <v>0.011095</v>
       </c>
     </row>
     <row r="951">
@@ -12793,7 +12793,7 @@
         <v>301</v>
       </c>
       <c r="C952" t="n">
-        <v>0.011253</v>
+        <v>0.01125</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>302</v>
       </c>
       <c r="C953" t="n">
-        <v>0.011342</v>
+        <v>0.011354</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>303</v>
       </c>
       <c r="C954" t="n">
-        <v>0.011541</v>
+        <v>0.011539</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>304</v>
       </c>
       <c r="C955" t="n">
-        <v>0.011684</v>
+        <v>0.011696</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>305</v>
       </c>
       <c r="C956" t="n">
-        <v>0.012034</v>
+        <v>0.012035</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>306</v>
       </c>
       <c r="C957" t="n">
-        <v>0.012333</v>
+        <v>0.012331</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>307</v>
       </c>
       <c r="C958" t="n">
-        <v>0.012399</v>
+        <v>0.012402</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>308</v>
       </c>
       <c r="C959" t="n">
-        <v>0.012556</v>
+        <v>0.012555</v>
       </c>
     </row>
     <row r="960">
@@ -12910,7 +12910,7 @@
         <v>310</v>
       </c>
       <c r="C961" t="n">
-        <v>0.013068</v>
+        <v>0.013066</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>311</v>
       </c>
       <c r="C962" t="n">
-        <v>0.013135</v>
+        <v>0.013145</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>312</v>
       </c>
       <c r="C963" t="n">
-        <v>0.013141</v>
+        <v>0.013169</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>313</v>
       </c>
       <c r="C964" t="n">
-        <v>0.013573</v>
+        <v>0.01357</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>314</v>
       </c>
       <c r="C965" t="n">
-        <v>0.013727</v>
+        <v>0.013723</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>315</v>
       </c>
       <c r="C966" t="n">
-        <v>0.014168</v>
+        <v>0.014166</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>316</v>
       </c>
       <c r="C967" t="n">
-        <v>0.014321</v>
+        <v>0.014317</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>317</v>
       </c>
       <c r="C968" t="n">
-        <v>0.01437</v>
+        <v>0.014389</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>318</v>
       </c>
       <c r="C969" t="n">
-        <v>0.014393</v>
+        <v>0.014396</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>319</v>
       </c>
       <c r="C970" t="n">
-        <v>0.014414</v>
+        <v>0.014432</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>320</v>
       </c>
       <c r="C971" t="n">
-        <v>0.014568</v>
+        <v>0.014566</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>321</v>
       </c>
       <c r="C972" t="n">
-        <v>0.01491</v>
+        <v>0.014938</v>
       </c>
     </row>
     <row r="973">
@@ -13079,7 +13079,7 @@
         <v>323</v>
       </c>
       <c r="C974" t="n">
-        <v>0.015121</v>
+        <v>0.015124</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>324</v>
       </c>
       <c r="C975" t="n">
-        <v>0.015169</v>
+        <v>0.015189</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>325</v>
       </c>
       <c r="C976" t="n">
-        <v>0.015579</v>
+        <v>0.01558</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>326</v>
       </c>
       <c r="C977" t="n">
-        <v>0.015727</v>
+        <v>0.015734</v>
       </c>
     </row>
     <row r="978">
@@ -13144,7 +13144,7 @@
         <v>328</v>
       </c>
       <c r="C979" t="n">
-        <v>0.016642</v>
+        <v>0.016638</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>329</v>
       </c>
       <c r="C980" t="n">
-        <v>0.016668</v>
+        <v>0.01669</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>330</v>
       </c>
       <c r="C981" t="n">
-        <v>0.016786</v>
+        <v>0.016794</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>331</v>
       </c>
       <c r="C982" t="n">
-        <v>0.016994</v>
+        <v>0.016995</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>332</v>
       </c>
       <c r="C983" t="n">
-        <v>0.017065</v>
+        <v>0.017078</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>333</v>
       </c>
       <c r="C984" t="n">
-        <v>0.01735</v>
+        <v>0.017368</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>334</v>
       </c>
       <c r="C985" t="n">
-        <v>0.017682</v>
+        <v>0.017679</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>335</v>
       </c>
       <c r="C986" t="n">
-        <v>0.017739</v>
+        <v>0.017736</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>336</v>
       </c>
       <c r="C987" t="n">
-        <v>0.017965</v>
+        <v>0.017995</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>337</v>
       </c>
       <c r="C988" t="n">
-        <v>0.017997</v>
+        <v>0.018009</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>338</v>
       </c>
       <c r="C989" t="n">
-        <v>0.018664</v>
+        <v>0.018682</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>339</v>
       </c>
       <c r="C990" t="n">
-        <v>0.018763</v>
+        <v>0.018758</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>340</v>
       </c>
       <c r="C991" t="n">
-        <v>0.018991</v>
+        <v>0.018985</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>341</v>
       </c>
       <c r="C992" t="n">
-        <v>0.019265</v>
+        <v>0.019261</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>342</v>
       </c>
       <c r="C993" t="n">
-        <v>0.019384</v>
+        <v>0.01938</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>343</v>
       </c>
       <c r="C994" t="n">
-        <v>0.019403</v>
+        <v>0.019399</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>344</v>
       </c>
       <c r="C995" t="n">
-        <v>0.019567</v>
+        <v>0.019565</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>345</v>
       </c>
       <c r="C996" t="n">
-        <v>0.019647</v>
+        <v>0.019642</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>346</v>
       </c>
       <c r="C997" t="n">
-        <v>0.019796</v>
+        <v>0.019815</v>
       </c>
     </row>
     <row r="998">
@@ -13391,7 +13391,7 @@
         <v>347</v>
       </c>
       <c r="C998" t="n">
-        <v>0.019995</v>
+        <v>0.020003</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>348</v>
       </c>
       <c r="C999" t="n">
-        <v>0.020219</v>
+        <v>0.020214</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>349</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.020969</v>
+        <v>0.020965</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>350</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.021125</v>
+        <v>0.021134</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>351</v>
       </c>
       <c r="C1002" t="n">
-        <v>0.021422</v>
+        <v>0.021417</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>352</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.021666</v>
+        <v>0.021699</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>353</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.021913</v>
+        <v>0.021923</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>354</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.022087</v>
+        <v>0.022106</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>355</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.022703</v>
+        <v>0.022697</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>356</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.022809</v>
+        <v>0.022876</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>357</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.0229</v>
+        <v>0.022898</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>358</v>
       </c>
       <c r="C1009" t="n">
-        <v>0.023248</v>
+        <v>0.023262</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>359</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.0237</v>
+        <v>0.023694</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>360</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.023713</v>
+        <v>0.023753</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>361</v>
       </c>
       <c r="C1012" t="n">
-        <v>0.023984</v>
+        <v>0.023994</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>362</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.024138</v>
+        <v>0.02419</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>363</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.024319</v>
+        <v>0.024313</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>364</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.024465</v>
+        <v>0.024497</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>365</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.024706</v>
+        <v>0.024715</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>366</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.024898</v>
+        <v>0.024903</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>367</v>
       </c>
       <c r="C1018" t="n">
-        <v>0.024943</v>
+        <v>0.025004</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>368</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.025315</v>
+        <v>0.02533</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>369</v>
       </c>
       <c r="C1020" t="n">
-        <v>0.02533</v>
+        <v>0.02537</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>370</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.025789</v>
+        <v>0.025782</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>371</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.025845</v>
+        <v>0.025843</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>372</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.025973</v>
+        <v>0.025966</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>373</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.026024</v>
+        <v>0.026021</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>374</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.026398</v>
+        <v>0.026403</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>375</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.026496</v>
+        <v>0.026494</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>376</v>
       </c>
       <c r="C1027" t="n">
-        <v>0.026581</v>
+        <v>0.026603</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>377</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.026742</v>
+        <v>0.026757</v>
       </c>
     </row>
     <row r="1029">
@@ -13807,7 +13807,7 @@
         <v>379</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.026969</v>
+        <v>0.026994</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>380</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.028562</v>
+        <v>0.028554</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>381</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.028587</v>
+        <v>0.028582</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>382</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.028712</v>
+        <v>0.028711</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>383</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.02906</v>
+        <v>0.029053</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>384</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.029115</v>
+        <v>0.029112</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>385</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.029221</v>
+        <v>0.029242</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>386</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.029223</v>
+        <v>0.029244</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>387</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.029686</v>
+        <v>0.029691</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>388</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.029721</v>
+        <v>0.029713</v>
       </c>
     </row>
     <row r="1040">
@@ -13950,7 +13950,7 @@
         <v>390</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.030234</v>
+        <v>0.030287</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>391</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.030472</v>
+        <v>0.030464</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>392</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.030577</v>
+        <v>0.030569</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>393</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.0311</v>
+        <v>0.031105</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>394</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.031485</v>
+        <v>0.031559</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>395</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.031591</v>
+        <v>0.031585</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>396</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.031638</v>
+        <v>0.031701</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>397</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.031648</v>
+        <v>0.031714</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>398</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.031922</v>
+        <v>0.031917</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>399</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.032209</v>
+        <v>0.0322</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>400</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.032512</v>
+        <v>0.032516</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>401</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.03267</v>
+        <v>0.032692</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>402</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.032696</v>
+        <v>0.032708</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>403</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.032866</v>
+        <v>0.032917</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>404</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.033102</v>
+        <v>0.033093</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>405</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.033334</v>
+        <v>0.033345</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>406</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.033539</v>
+        <v>0.033533</v>
       </c>
     </row>
     <row r="1058">
@@ -14184,7 +14184,7 @@
         <v>408</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.033744</v>
+        <v>0.033775</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>409</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.033899</v>
+        <v>0.033901</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>410</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.034029</v>
+        <v>0.034063</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>411</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.034155</v>
+        <v>0.034171</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>412</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.034265</v>
+        <v>0.034255</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>413</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.035101</v>
+        <v>0.035095</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>414</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.035257</v>
+        <v>0.035281</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>415</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.035463</v>
+        <v>0.035453</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>416</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.03553</v>
+        <v>0.035531</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>417</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.035825</v>
+        <v>0.035829</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>418</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.035996</v>
+        <v>0.035988</v>
       </c>
     </row>
     <row r="1070">
@@ -14340,7 +14340,7 @@
         <v>420</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.036072</v>
+        <v>0.036084</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>421</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.036734</v>
+        <v>0.036727</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>422</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.036757</v>
+        <v>0.036773</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>423</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.036783</v>
+        <v>0.036785</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>424</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.037385</v>
+        <v>0.037413</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>425</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.037737</v>
+        <v>0.037832</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>426</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.038258</v>
+        <v>0.038276</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>427</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.038576</v>
+        <v>0.038565</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>428</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.038654</v>
+        <v>0.038651</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>429</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.039295</v>
+        <v>0.039375</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>430</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.039584</v>
+        <v>0.039592</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>431</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.039714</v>
+        <v>0.03971</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>432</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.039789</v>
+        <v>0.039788</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>433</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.040049</v>
+        <v>0.040053</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>434</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.040049</v>
+        <v>0.040061</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>435</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.040072</v>
+        <v>0.040097</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>436</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.04093</v>
+        <v>0.04092</v>
       </c>
     </row>
     <row r="1088">
@@ -14574,7 +14574,7 @@
         <v>438</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.04097</v>
+        <v>0.040959</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>439</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.040987</v>
+        <v>0.041013</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>440</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.041025</v>
+        <v>0.04103</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>441</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.042605</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>442</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.042862</v>
+        <v>0.042868</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>443</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.043146</v>
+        <v>0.043143</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>444</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.043512</v>
+        <v>0.043556</v>
       </c>
     </row>
     <row r="1096">
@@ -14678,7 +14678,7 @@
         <v>446</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.043818</v>
+        <v>0.043811</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>447</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.043944</v>
+        <v>0.043938</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>448</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.044036</v>
+        <v>0.044127</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>449</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.044567</v>
+        <v>0.04456</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>450</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.044655</v>
+        <v>0.044657</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>451</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.044707</v>
+        <v>0.044694</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>452</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.044908</v>
+        <v>0.044957</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>453</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.044965</v>
+        <v>0.044958</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>454</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.045098</v>
+        <v>0.045093</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>455</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.045206</v>
+        <v>0.045212</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>456</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.045277</v>
+        <v>0.045367</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>457</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.045378</v>
+        <v>0.045411</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>458</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.045587</v>
+        <v>0.045575</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>459</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.046203</v>
+        <v>0.046192</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>460</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.046246</v>
+        <v>0.046234</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>461</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.046478</v>
+        <v>0.046507</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>462</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.046904</v>
+        <v>0.046923</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>463</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.047062</v>
+        <v>0.047048</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>464</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.04744</v>
+        <v>0.047573</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>465</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.047589</v>
+        <v>0.047576</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>466</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.047682</v>
+        <v>0.047684</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>467</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.048681</v>
+        <v>0.048673</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>468</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.049252</v>
+        <v>0.049257</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>469</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.050171</v>
+        <v>0.050167</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>470</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.050542</v>
+        <v>0.050663</v>
       </c>
     </row>
     <row r="1122">
@@ -15003,7 +15003,7 @@
         <v>471</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.050588</v>
+        <v>0.050737</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>472</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.050752</v>
+        <v>0.050857</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>473</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.050905</v>
+        <v>0.050903</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>474</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.050916</v>
+        <v>0.050903</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>475</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.051922</v>
+        <v>0.052036</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>476</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.052557</v>
+        <v>0.052567</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>477</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.052938</v>
+        <v>0.052978</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>478</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.053051</v>
+        <v>0.053063</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>479</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.053156</v>
+        <v>0.053223</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>480</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.053755</v>
+        <v>0.053777</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>481</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.053787</v>
+        <v>0.053888</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>482</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.054241</v>
+        <v>0.054272</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>483</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.054358</v>
+        <v>0.054348</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>484</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.054421</v>
+        <v>0.054405</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>485</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.054546</v>
+        <v>0.054564</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>486</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.054584</v>
+        <v>0.054603</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>487</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.05465</v>
+        <v>0.054654</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>488</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.054655</v>
+        <v>0.054779</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>489</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.054783</v>
+        <v>0.054789</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>490</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.05515</v>
+        <v>0.055135</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>491</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.055443</v>
+        <v>0.055428</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>492</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.056085</v>
+        <v>0.056147</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>493</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.056198</v>
+        <v>0.056192</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>494</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.056566</v>
+        <v>0.056577</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>495</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.056756</v>
+        <v>0.056744</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>496</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.057161</v>
+        <v>0.057145</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>497</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.057745</v>
+        <v>0.057797</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>498</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.057938</v>
+        <v>0.057982</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>499</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.05799</v>
+        <v>0.058013</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>500</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.058953</v>
+        <v>0.058939</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>501</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.059816</v>
+        <v>0.059817</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>502</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.059832</v>
+        <v>0.059833</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>503</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.059881</v>
+        <v>0.059921</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>504</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.060024</v>
+        <v>0.060028</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>505</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.060419</v>
+        <v>0.060447</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>506</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.060627</v>
+        <v>0.060611</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>507</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.060836</v>
+        <v>0.060835</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>508</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.062016</v>
+        <v>0.062004</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>509</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.062023</v>
+        <v>0.062033</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>510</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.063151</v>
+        <v>0.063225</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>511</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.064138</v>
+        <v>0.064293</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>512</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.064303</v>
+        <v>0.064488</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>513</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.064461</v>
+        <v>0.06456099999999999</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>514</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.065174</v>
+        <v>0.065307</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>515</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.065481</v>
+        <v>0.065565</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>516</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.065664</v>
+        <v>0.065675</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>517</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.06615500000000001</v>
+        <v>0.06616900000000001</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>518</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.066357</v>
+        <v>0.066445</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>519</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.067298</v>
+        <v>0.067291</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>520</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.06744799999999999</v>
+        <v>0.06744600000000001</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>521</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.068476</v>
+        <v>0.068499</v>
       </c>
     </row>
     <row r="1173">
@@ -15679,7 +15679,7 @@
         <v>523</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.06872399999999999</v>
+        <v>0.06870800000000001</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>524</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.068939</v>
+        <v>0.06891899999999999</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>525</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.069462</v>
+        <v>0.069454</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>526</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.069886</v>
+        <v>0.069866</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>527</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.070033</v>
+        <v>0.07020899999999999</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>528</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.070504</v>
+        <v>0.07048699999999999</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>529</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.070789</v>
+        <v>0.070872</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>530</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.07142800000000001</v>
+        <v>0.07152500000000001</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>531</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.071787</v>
+        <v>0.07188899999999999</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>532</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.07252599999999999</v>
+        <v>0.072573</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>533</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.072738</v>
+        <v>0.072728</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>534</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.072862</v>
+        <v>0.07285999999999999</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>535</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.07292999999999999</v>
+        <v>0.073058</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>536</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.07394199999999999</v>
+        <v>0.073946</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>537</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.07396800000000001</v>
+        <v>0.073951</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>538</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.07464999999999999</v>
+        <v>0.074644</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>539</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.074724</v>
+        <v>0.074707</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>540</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.075501</v>
+        <v>0.075504</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>541</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.075637</v>
+        <v>0.075714</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>542</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.075781</v>
+        <v>0.07581300000000001</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>543</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.07661800000000001</v>
+        <v>0.076651</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>544</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.07746500000000001</v>
+        <v>0.077533</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>545</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.07874200000000001</v>
+        <v>0.07872700000000001</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>546</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.078768</v>
+        <v>0.078767</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>547</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.07935200000000001</v>
+        <v>0.079348</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>548</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.07982400000000001</v>
+        <v>0.079834</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>549</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.080383</v>
+        <v>0.08036</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>550</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.080827</v>
+        <v>0.080845</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>551</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.081091</v>
+        <v>0.08128100000000001</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>552</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.081913</v>
+        <v>0.08189399999999999</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>553</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.08290400000000001</v>
+        <v>0.083069</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>554</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.08290699999999999</v>
+        <v>0.083133</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>555</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.08305999999999999</v>
+        <v>0.08314100000000001</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>556</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.08361</v>
+        <v>0.08361300000000001</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>557</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.083629</v>
+        <v>0.083665</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>558</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.085511</v>
+        <v>0.08566699999999999</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>559</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.085603</v>
+        <v>0.085799</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>560</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.086044</v>
+        <v>0.08607099999999999</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>561</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.08645600000000001</v>
+        <v>0.086447</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>562</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.087834</v>
+        <v>0.087812</v>
       </c>
     </row>
     <row r="1214">
@@ -16212,7 +16212,7 @@
         <v>564</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.088805</v>
+        <v>0.08880399999999999</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>565</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.088905</v>
+        <v>0.088922</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>566</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.091015</v>
+        <v>0.090993</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>567</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.092117</v>
+        <v>0.092151</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>568</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.09227299999999999</v>
+        <v>0.092318</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>569</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.09246799999999999</v>
+        <v>0.092442</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>570</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.093531</v>
+        <v>0.093721</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>571</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.09439500000000001</v>
+        <v>0.09481299999999999</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>572</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.09543</v>
+        <v>0.095403</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>573</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.09578299999999999</v>
+        <v>0.095761</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>574</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.095841</v>
+        <v>0.09593</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>575</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.096613</v>
+        <v>0.09658600000000001</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>576</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.097264</v>
+        <v>0.097386</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>577</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.0978</v>
+        <v>0.097841</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>578</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.09805700000000001</v>
+        <v>0.098048</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>579</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.099347</v>
+        <v>0.099486</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>580</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.099823</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>581</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.100432</v>
+        <v>0.100465</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>582</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.100487</v>
+        <v>0.10048</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>583</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.101613</v>
+        <v>0.101716</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>584</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.102349</v>
+        <v>0.102325</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>585</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.102395</v>
+        <v>0.10243</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>586</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.103921</v>
+        <v>0.103894</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>587</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.109265</v>
+        <v>0.109281</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>588</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.109542</v>
+        <v>0.109517</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>589</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.109547</v>
+        <v>0.10956</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>590</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.109593</v>
+        <v>0.109576</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>591</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.109882</v>
+        <v>0.109873</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>592</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.110574</v>
+        <v>0.110623</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>593</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.112118</v>
+        <v>0.112101</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>594</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.11398</v>
+        <v>0.113949</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>595</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.116061</v>
+        <v>0.116135</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>596</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.119087</v>
+        <v>0.119412</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>597</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.119619</v>
+        <v>0.119668</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>598</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.119653</v>
+        <v>0.119724</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>599</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.121035</v>
+        <v>0.121149</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>600</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.121528</v>
+        <v>0.121502</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>601</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.12322</v>
+        <v>0.123301</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>602</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.123557</v>
+        <v>0.123606</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>603</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.12615</v>
+        <v>0.126194</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>604</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.126728</v>
+        <v>0.127097</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>605</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.12749</v>
+        <v>0.127793</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>606</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.130624</v>
+        <v>0.130605</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>607</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.131116</v>
+        <v>0.131158</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>608</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.131371</v>
+        <v>0.131355</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>609</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.133053</v>
+        <v>0.133056</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>610</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.13632</v>
+        <v>0.136293</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>611</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.136322</v>
+        <v>0.136314</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>612</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.136884</v>
+        <v>0.136913</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>613</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.137248</v>
+        <v>0.137498</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>614</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.139299</v>
+        <v>0.139296</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>615</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.141219</v>
+        <v>0.141222</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>616</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.142442</v>
+        <v>0.142491</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>617</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.142822</v>
+        <v>0.142816</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>618</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.143551</v>
+        <v>0.143518</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>619</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.145185</v>
+        <v>0.145162</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>620</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.153528</v>
+        <v>0.153553</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>621</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.156252</v>
+        <v>0.156313</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>622</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.159995</v>
+        <v>0.16014</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>623</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.160384</v>
+        <v>0.160339</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>624</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.161266</v>
+        <v>0.161282</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>625</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.170738</v>
+        <v>0.170712</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>626</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.175768</v>
+        <v>0.175718</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>627</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.180637</v>
+        <v>0.180963</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>628</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.180855</v>
+        <v>0.181119</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>629</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.181561</v>
+        <v>0.181514</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>630</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.182641</v>
+        <v>0.182595</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>631</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.186446</v>
+        <v>0.186411</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>632</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.187043</v>
+        <v>0.187097</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>633</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.188646</v>
+        <v>0.188841</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>634</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.189913</v>
+        <v>0.19019</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>635</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.197461</v>
+        <v>0.197482</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>636</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.200467</v>
+        <v>0.200888</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>637</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.207966</v>
+        <v>0.207983</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>638</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.221318</v>
+        <v>0.221327</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>639</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.245136</v>
+        <v>0.245114</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>640</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.248924</v>
+        <v>0.249245</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>641</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.260321</v>
+        <v>0.260509</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>642</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>643</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.266352</v>
+        <v>0.2669</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>644</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.274368</v>
+        <v>0.274307</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>645</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>646</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.347965</v>
+        <v>0.347869</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>647</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.359432</v>
+        <v>0.35942</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>648</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.503824</v>
+        <v>0.5037</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_plot_data.xlsx
+++ b/vignettes/vignette-1/distribution_plot_data.xlsx
@@ -6644,7 +6644,7 @@
         <v>477</v>
       </c>
       <c r="C479" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
     </row>
     <row r="480">
@@ -6657,7 +6657,7 @@
         <v>478</v>
       </c>
       <c r="C480" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
     </row>
     <row r="481">
@@ -6670,7 +6670,7 @@
         <v>479</v>
       </c>
       <c r="C481" t="n">
-        <v>0.056785</v>
+        <v>0.057942</v>
       </c>
     </row>
     <row r="482">
@@ -6683,7 +6683,7 @@
         <v>480</v>
       </c>
       <c r="C482" t="n">
-        <v>0.057942</v>
+        <v>0.05854</v>
       </c>
     </row>
     <row r="483">
@@ -6696,7 +6696,7 @@
         <v>481</v>
       </c>
       <c r="C483" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
     </row>
     <row r="484">
@@ -6709,7 +6709,7 @@
         <v>482</v>
       </c>
       <c r="C484" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
     </row>
     <row r="485">
@@ -6722,7 +6722,7 @@
         <v>483</v>
       </c>
       <c r="C485" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
     </row>
     <row r="486">
@@ -6735,7 +6735,7 @@
         <v>484</v>
       </c>
       <c r="C486" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
     </row>
     <row r="487">
@@ -6748,7 +6748,7 @@
         <v>485</v>
       </c>
       <c r="C487" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
     </row>
     <row r="488">
@@ -6761,7 +6761,7 @@
         <v>486</v>
       </c>
       <c r="C488" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
     </row>
     <row r="489">
@@ -6774,7 +6774,7 @@
         <v>487</v>
       </c>
       <c r="C489" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
     </row>
     <row r="490">
@@ -6787,7 +6787,7 @@
         <v>488</v>
       </c>
       <c r="C490" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
     </row>
     <row r="491">
@@ -6800,7 +6800,7 @@
         <v>489</v>
       </c>
       <c r="C491" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
     </row>
     <row r="492">
@@ -6813,7 +6813,7 @@
         <v>490</v>
       </c>
       <c r="C492" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
     </row>
     <row r="493">
@@ -6826,7 +6826,7 @@
         <v>491</v>
       </c>
       <c r="C493" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
     </row>
     <row r="494">
@@ -6839,7 +6839,7 @@
         <v>492</v>
       </c>
       <c r="C494" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
     </row>
     <row r="495">
@@ -6852,7 +6852,7 @@
         <v>493</v>
       </c>
       <c r="C495" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
     </row>
     <row r="496">
@@ -6865,7 +6865,7 @@
         <v>494</v>
       </c>
       <c r="C496" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
     </row>
     <row r="497">
@@ -6878,7 +6878,7 @@
         <v>495</v>
       </c>
       <c r="C497" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
     </row>
     <row r="498">
@@ -6891,7 +6891,7 @@
         <v>496</v>
       </c>
       <c r="C498" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
     </row>
     <row r="499">
@@ -6904,7 +6904,7 @@
         <v>497</v>
       </c>
       <c r="C499" t="n">
-        <v>0.062168</v>
+        <v>0.06263299999999999</v>
       </c>
     </row>
     <row r="500">
@@ -6917,7 +6917,7 @@
         <v>498</v>
       </c>
       <c r="C500" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
     </row>
     <row r="501">
@@ -6930,7 +6930,7 @@
         <v>499</v>
       </c>
       <c r="C501" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
     </row>
     <row r="502">
@@ -6943,7 +6943,7 @@
         <v>500</v>
       </c>
       <c r="C502" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
     </row>
     <row r="503">
@@ -6956,7 +6956,7 @@
         <v>501</v>
       </c>
       <c r="C503" t="n">
-        <v>0.064842</v>
+        <v>0.06555900000000001</v>
       </c>
     </row>
     <row r="504">
@@ -6969,7 +6969,7 @@
         <v>502</v>
       </c>
       <c r="C504" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067176</v>
       </c>
     </row>
     <row r="505">
@@ -6982,7 +6982,7 @@
         <v>503</v>
       </c>
       <c r="C505" t="n">
-        <v>0.067176</v>
+        <v>0.06736399999999999</v>
       </c>
     </row>
     <row r="506">
@@ -6995,7 +6995,7 @@
         <v>504</v>
       </c>
       <c r="C506" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067375</v>
       </c>
     </row>
     <row r="507">
@@ -7008,7 +7008,7 @@
         <v>505</v>
       </c>
       <c r="C507" t="n">
-        <v>0.067375</v>
+        <v>0.067555</v>
       </c>
     </row>
     <row r="508">
@@ -7021,7 +7021,7 @@
         <v>506</v>
       </c>
       <c r="C508" t="n">
-        <v>0.067555</v>
+        <v>0.067604</v>
       </c>
     </row>
     <row r="509">
@@ -7034,7 +7034,7 @@
         <v>507</v>
       </c>
       <c r="C509" t="n">
-        <v>0.067604</v>
+        <v>0.067644</v>
       </c>
     </row>
     <row r="510">
@@ -7047,7 +7047,7 @@
         <v>508</v>
       </c>
       <c r="C510" t="n">
-        <v>0.067644</v>
+        <v>0.068111</v>
       </c>
     </row>
     <row r="511">
@@ -7060,7 +7060,7 @@
         <v>509</v>
       </c>
       <c r="C511" t="n">
-        <v>0.068111</v>
+        <v>0.068538</v>
       </c>
     </row>
     <row r="512">
@@ -7073,7 +7073,7 @@
         <v>510</v>
       </c>
       <c r="C512" t="n">
-        <v>0.068538</v>
+        <v>0.068601</v>
       </c>
     </row>
     <row r="513">
@@ -7086,7 +7086,7 @@
         <v>511</v>
       </c>
       <c r="C513" t="n">
-        <v>0.068601</v>
+        <v>0.068845</v>
       </c>
     </row>
     <row r="514">
@@ -7099,7 +7099,7 @@
         <v>512</v>
       </c>
       <c r="C514" t="n">
-        <v>0.068845</v>
+        <v>0.068939</v>
       </c>
     </row>
     <row r="515">
@@ -7112,7 +7112,7 @@
         <v>513</v>
       </c>
       <c r="C515" t="n">
-        <v>0.068939</v>
+        <v>0.06909</v>
       </c>
     </row>
     <row r="516">
@@ -7125,7 +7125,7 @@
         <v>514</v>
       </c>
       <c r="C516" t="n">
-        <v>0.06909</v>
+        <v>0.069253</v>
       </c>
     </row>
     <row r="517">
@@ -7138,7 +7138,7 @@
         <v>515</v>
       </c>
       <c r="C517" t="n">
-        <v>0.069253</v>
+        <v>0.070214</v>
       </c>
     </row>
     <row r="518">
@@ -7151,7 +7151,7 @@
         <v>516</v>
       </c>
       <c r="C518" t="n">
-        <v>0.070214</v>
+        <v>0.070659</v>
       </c>
     </row>
     <row r="519">
@@ -7164,7 +7164,7 @@
         <v>517</v>
       </c>
       <c r="C519" t="n">
-        <v>0.070659</v>
+        <v>0.071449</v>
       </c>
     </row>
     <row r="520">
@@ -8802,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.274583</v>
+        <v>-0.27477</v>
       </c>
     </row>
     <row r="646">
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.173782</v>
+        <v>-0.173797</v>
       </c>
     </row>
     <row r="647">
@@ -8828,7 +8828,7 @@
         <v>2</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.170501</v>
+        <v>-0.17049</v>
       </c>
     </row>
     <row r="648">
@@ -8841,7 +8841,7 @@
         <v>3</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.143631</v>
+        <v>-0.143644</v>
       </c>
     </row>
     <row r="649">
@@ -8854,7 +8854,7 @@
         <v>4</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.123794</v>
+        <v>-0.12382</v>
       </c>
     </row>
     <row r="650">
@@ -8867,7 +8867,7 @@
         <v>5</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.119245</v>
+        <v>-0.119254</v>
       </c>
     </row>
     <row r="651">
@@ -8880,7 +8880,7 @@
         <v>6</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.116456</v>
+        <v>-0.116447</v>
       </c>
     </row>
     <row r="652">
@@ -8893,7 +8893,7 @@
         <v>7</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.112842</v>
+        <v>-0.11285</v>
       </c>
     </row>
     <row r="653">
@@ -8906,7 +8906,7 @@
         <v>8</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.111982</v>
+        <v>-0.111977</v>
       </c>
     </row>
     <row r="654">
@@ -8932,7 +8932,7 @@
         <v>10</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.106204</v>
+        <v>-0.106196</v>
       </c>
     </row>
     <row r="656">
@@ -8945,7 +8945,7 @@
         <v>11</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.105785</v>
+        <v>-0.105779</v>
       </c>
     </row>
     <row r="657">
@@ -8958,7 +8958,7 @@
         <v>12</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.105496</v>
+        <v>-0.105497</v>
       </c>
     </row>
     <row r="658">
@@ -8984,7 +8984,7 @@
         <v>14</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.104073</v>
+        <v>-0.104068</v>
       </c>
     </row>
     <row r="660">
@@ -8997,7 +8997,7 @@
         <v>15</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.103936</v>
+        <v>-0.104033</v>
       </c>
     </row>
     <row r="661">
@@ -9010,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.101231</v>
+        <v>-0.101255</v>
       </c>
     </row>
     <row r="662">
@@ -9023,7 +9023,7 @@
         <v>17</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.097799</v>
+        <v>-0.097791</v>
       </c>
     </row>
     <row r="663">
@@ -9036,7 +9036,7 @@
         <v>18</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.097792</v>
+        <v>-0.097788</v>
       </c>
     </row>
     <row r="664">
@@ -9049,7 +9049,7 @@
         <v>19</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.096553</v>
+        <v>-0.09654799999999999</v>
       </c>
     </row>
     <row r="665">
@@ -9062,7 +9062,7 @@
         <v>20</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.09508900000000001</v>
+        <v>-0.095086</v>
       </c>
     </row>
     <row r="666">
@@ -9075,7 +9075,7 @@
         <v>21</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.09481100000000001</v>
+        <v>-0.09484099999999999</v>
       </c>
     </row>
     <row r="667">
@@ -9088,7 +9088,7 @@
         <v>22</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.094693</v>
+        <v>-0.09468500000000001</v>
       </c>
     </row>
     <row r="668">
@@ -9101,7 +9101,7 @@
         <v>23</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.09399</v>
+        <v>-0.093984</v>
       </c>
     </row>
     <row r="669">
@@ -9114,7 +9114,7 @@
         <v>24</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.092402</v>
+        <v>-0.092498</v>
       </c>
     </row>
     <row r="670">
@@ -9127,7 +9127,7 @@
         <v>25</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.09168800000000001</v>
+        <v>-0.09178699999999999</v>
       </c>
     </row>
     <row r="671">
@@ -9140,7 +9140,7 @@
         <v>26</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.090979</v>
+        <v>-0.090974</v>
       </c>
     </row>
     <row r="672">
@@ -9153,7 +9153,7 @@
         <v>27</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.09017500000000001</v>
+        <v>-0.090173</v>
       </c>
     </row>
     <row r="673">
@@ -9166,7 +9166,7 @@
         <v>28</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.08975900000000001</v>
+        <v>-0.089758</v>
       </c>
     </row>
     <row r="674">
@@ -9179,7 +9179,7 @@
         <v>29</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.087905</v>
+        <v>-0.088001</v>
       </c>
     </row>
     <row r="675">
@@ -9192,7 +9192,7 @@
         <v>30</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.086115</v>
+        <v>-0.086108</v>
       </c>
     </row>
     <row r="676">
@@ -9205,7 +9205,7 @@
         <v>31</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.085406</v>
+        <v>-0.085497</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>32</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.084124</v>
+        <v>-0.084212</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>33</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.08387500000000001</v>
+        <v>-0.083874</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>34</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.080237</v>
+        <v>-0.080259</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>35</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.079844</v>
+        <v>-0.079876</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>36</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.07933</v>
+        <v>-0.07937</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>37</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.077891</v>
+        <v>-0.07792300000000001</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>38</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.07580099999999999</v>
+        <v>-0.075807</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>39</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.073181</v>
+        <v>-0.073175</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>40</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.072793</v>
+        <v>-0.072864</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>41</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.072558</v>
+        <v>-0.07255399999999999</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>42</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.070615</v>
+        <v>-0.07063899999999999</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>43</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.06964099999999999</v>
+        <v>-0.06963800000000001</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>44</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.06940300000000001</v>
+        <v>-0.06943299999999999</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>45</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.06782299999999999</v>
+        <v>-0.06782199999999999</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>46</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.067514</v>
+        <v>-0.06751</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>47</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.067175</v>
+        <v>-0.06716999999999999</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>48</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.06701600000000001</v>
+        <v>-0.067033</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>49</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.066965</v>
+        <v>-0.067011</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>50</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.066027</v>
+        <v>-0.066071</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>51</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.065182</v>
+        <v>-0.065208</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>52</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.06469900000000001</v>
+        <v>-0.064828</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>53</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.06421399999999999</v>
+        <v>-0.06421</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>54</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.063592</v>
+        <v>-0.063593</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>55</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.063239</v>
+        <v>-0.063245</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>56</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.062282</v>
+        <v>-0.06228</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>57</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.062103</v>
+        <v>-0.06211</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>58</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.061682</v>
+        <v>-0.061677</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>59</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.06104</v>
+        <v>-0.061039</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>60</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.060751</v>
+        <v>-0.060774</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>61</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.060544</v>
+        <v>-0.060545</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>62</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.059992</v>
+        <v>-0.059996</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>63</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.059833</v>
+        <v>-0.05983</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>64</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.059725</v>
+        <v>-0.059746</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>65</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.058043</v>
+        <v>-0.058038</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>66</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.057233</v>
+        <v>-0.057228</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>67</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.056186</v>
+        <v>-0.056182</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>68</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.055467</v>
+        <v>-0.055499</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>69</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.05517</v>
+        <v>-0.055166</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>70</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.055032</v>
+        <v>-0.055042</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>71</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.054964</v>
+        <v>-0.054982</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>72</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.054622</v>
+        <v>-0.05462</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>73</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.053765</v>
+        <v>-0.053774</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>74</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.053187</v>
+        <v>-0.053188</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>75</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.052977</v>
+        <v>-0.052988</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>76</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.052973</v>
+        <v>-0.05297</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>77</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.052605</v>
+        <v>-0.052601</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>78</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.052262</v>
+        <v>-0.05229</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>79</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.051801</v>
+        <v>-0.051832</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>80</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.051619</v>
+        <v>-0.051635</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>81</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.05127</v>
+        <v>-0.051266</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.051213</v>
+        <v>-0.051211</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>83</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.051133</v>
+        <v>-0.051129</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>84</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.050996</v>
+        <v>-0.051016</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>85</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.050716</v>
+        <v>-0.050712</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>86</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.050112</v>
+        <v>-0.05016</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>87</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.049628</v>
+        <v>-0.049635</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>88</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.049456</v>
+        <v>-0.049455</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>89</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.049111</v>
+        <v>-0.049183</v>
       </c>
     </row>
     <row r="735">
@@ -9985,7 +9985,7 @@
         <v>91</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.048525</v>
+        <v>-0.048529</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>92</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.048389</v>
+        <v>-0.048399</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>93</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.048133</v>
+        <v>-0.04813</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>94</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.047665</v>
+        <v>-0.047674</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>95</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.047065</v>
+        <v>-0.047074</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>96</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.046981</v>
+        <v>-0.047035</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>97</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.046933</v>
+        <v>-0.046938</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>98</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.045847</v>
+        <v>-0.045883</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>99</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.045758</v>
+        <v>-0.045755</v>
       </c>
     </row>
     <row r="745">
@@ -10115,7 +10115,7 @@
         <v>101</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.045575</v>
+        <v>-0.045578</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>102</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.045543</v>
+        <v>-0.04554</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>103</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.045295</v>
+        <v>-0.045327</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>104</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.044572</v>
+        <v>-0.04458</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>105</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.04434</v>
+        <v>-0.044347</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>106</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.044265</v>
+        <v>-0.044261</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>107</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.044109</v>
+        <v>-0.044105</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>108</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.04401</v>
+        <v>-0.044009</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>109</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.041939</v>
+        <v>-0.041937</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>110</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.040126</v>
+        <v>-0.040127</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>111</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.040123</v>
+        <v>-0.04012</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>112</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.03995</v>
+        <v>-0.039949</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>113</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.038532</v>
+        <v>-0.038529</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>114</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.038394</v>
+        <v>-0.038444</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>115</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.038055</v>
+        <v>-0.038061</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>116</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.037876</v>
+        <v>-0.037873</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>117</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.037423</v>
+        <v>-0.037436</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>118</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.036414</v>
+        <v>-0.036411</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>119</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.03637</v>
+        <v>-0.036399</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>120</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.036363</v>
+        <v>-0.036384</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>121</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.036204</v>
+        <v>-0.036225</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>122</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.035299</v>
+        <v>-0.035302</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>123</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.03418</v>
+        <v>-0.034188</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>124</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.033959</v>
+        <v>-0.033997</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>125</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.033797</v>
+        <v>-0.033831</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>126</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.033763</v>
+        <v>-0.033761</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>127</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.032901</v>
+        <v>-0.032909</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>128</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.032226</v>
+        <v>-0.032281</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>129</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.032202</v>
+        <v>-0.032199</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>130</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.032049</v>
+        <v>-0.03205</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>131</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.03174</v>
+        <v>-0.031746</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>132</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.031228</v>
+        <v>-0.031293</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>133</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.030592</v>
+        <v>-0.030612</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>134</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.030002</v>
+        <v>-0.030003</v>
       </c>
     </row>
     <row r="780">
@@ -10570,7 +10570,7 @@
         <v>136</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.029386</v>
+        <v>-0.029389</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>137</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.02908</v>
+        <v>-0.029093</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>138</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.028759</v>
+        <v>-0.028762</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>139</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.028171</v>
+        <v>-0.028169</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>140</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.028144</v>
+        <v>-0.028143</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>141</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.02813</v>
+        <v>-0.028128</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>142</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.028006</v>
+        <v>-0.028004</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>143</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.027605</v>
+        <v>-0.027619</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>144</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.027556</v>
+        <v>-0.027557</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>145</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.02661</v>
+        <v>-0.026608</v>
       </c>
     </row>
     <row r="791">
@@ -10713,7 +10713,7 @@
         <v>147</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.025426</v>
+        <v>-0.025424</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>148</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.025315</v>
+        <v>-0.025317</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>149</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.024987</v>
+        <v>-0.024986</v>
       </c>
     </row>
     <row r="795">
@@ -10765,7 +10765,7 @@
         <v>151</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.023974</v>
+        <v>-0.023981</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>152</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.023971</v>
+        <v>-0.023969</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>153</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.023705</v>
+        <v>-0.023711</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>154</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.023564</v>
+        <v>-0.023568</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>155</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.022067</v>
+        <v>-0.022075</v>
       </c>
     </row>
     <row r="801">
@@ -10843,7 +10843,7 @@
         <v>157</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.021957</v>
+        <v>-0.021956</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>158</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.021771</v>
+        <v>-0.021777</v>
       </c>
     </row>
     <row r="804">
@@ -10882,7 +10882,7 @@
         <v>160</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.020983</v>
+        <v>-0.020982</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>161</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.020828</v>
+        <v>-0.020826</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>162</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.020601</v>
+        <v>-0.020634</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>163</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.0202</v>
+        <v>-0.020199</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>164</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.019927</v>
+        <v>-0.019926</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>165</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.019726</v>
+        <v>-0.019725</v>
       </c>
     </row>
     <row r="811">
@@ -10973,7 +10973,7 @@
         <v>167</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.01936</v>
+        <v>-0.019364</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>168</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.019253</v>
+        <v>-0.019258</v>
       </c>
     </row>
     <row r="814">
@@ -11012,7 +11012,7 @@
         <v>170</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.018838</v>
+        <v>-0.018837</v>
       </c>
     </row>
     <row r="816">
@@ -11038,7 +11038,7 @@
         <v>172</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.018375</v>
+        <v>-0.018374</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>173</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.018332</v>
+        <v>-0.018335</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>174</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.017954</v>
+        <v>-0.017956</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>175</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.017831</v>
+        <v>-0.01783</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>176</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.0178</v>
+        <v>-0.017798</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>177</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.017334</v>
+        <v>-0.017338</v>
       </c>
     </row>
     <row r="823">
@@ -11129,7 +11129,7 @@
         <v>179</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.017155</v>
+        <v>-0.017167</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>180</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.016714</v>
+        <v>-0.016716</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>181</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.015975</v>
+        <v>-0.015974</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>182</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.014972</v>
+        <v>-0.014971</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>183</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.014919</v>
+        <v>-0.014934</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>184</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.014708</v>
+        <v>-0.01472</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>185</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.013864</v>
+        <v>-0.01387</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>186</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.013757</v>
+        <v>-0.013762</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>187</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.013268</v>
+        <v>-0.013267</v>
       </c>
     </row>
     <row r="833">
@@ -11272,7 +11272,7 @@
         <v>190</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.012567</v>
+        <v>-0.012569</v>
       </c>
     </row>
     <row r="836">
@@ -11311,7 +11311,7 @@
         <v>193</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.012178</v>
+        <v>-0.012179</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>194</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.012011</v>
+        <v>-0.012013</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>195</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.011797</v>
+        <v>-0.011804</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>196</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.011699</v>
+        <v>-0.011714</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>197</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.011479</v>
+        <v>-0.011485</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>198</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.01086</v>
+        <v>-0.010861</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>199</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.010564</v>
+        <v>-0.010566</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>200</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.009693999999999999</v>
+        <v>-0.009693</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>201</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.009655</v>
+        <v>-0.009671000000000001</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>202</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.009279000000000001</v>
+        <v>-0.009278</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>203</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.009148</v>
+        <v>-0.009150999999999999</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>204</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.009112</v>
+        <v>-0.009115</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>205</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.008871</v>
+        <v>-0.008872</v>
       </c>
     </row>
     <row r="851">
@@ -11493,7 +11493,7 @@
         <v>207</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.008734</v>
+        <v>-0.008732999999999999</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>208</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.007899</v>
+        <v>-0.007903</v>
       </c>
     </row>
     <row r="854">
@@ -11532,7 +11532,7 @@
         <v>210</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.007425</v>
+        <v>-0.007426</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>211</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.007353</v>
+        <v>-0.007352</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>212</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.007159</v>
+        <v>-0.007162</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>213</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.007041</v>
+        <v>-0.007042</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>214</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.006925</v>
+        <v>-0.006926</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>215</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.006427</v>
+        <v>-0.006435</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>216</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.006356</v>
+        <v>-0.006357</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>217</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.005886</v>
+        <v>-0.005887</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>218</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.005712</v>
+        <v>-0.005718</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>219</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.005659</v>
+        <v>-0.00566</v>
       </c>
     </row>
     <row r="865">
@@ -11688,7 +11688,7 @@
         <v>222</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.004805</v>
+        <v>-0.004808</v>
       </c>
     </row>
     <row r="868">
@@ -11714,7 +11714,7 @@
         <v>224</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.004564</v>
+        <v>-0.004566</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>225</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.004261</v>
+        <v>-0.004263</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>226</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.004258</v>
+        <v>-0.004261</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>227</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.004228</v>
+        <v>-0.004229</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>228</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.0042</v>
+        <v>-0.004201</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>229</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.004088</v>
+        <v>-0.004089</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>230</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.003812</v>
+        <v>-0.003815</v>
       </c>
     </row>
     <row r="876">
@@ -11844,7 +11844,7 @@
         <v>234</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.002756</v>
+        <v>-0.002759</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>235</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.002746</v>
+        <v>-0.002747</v>
       </c>
     </row>
     <row r="881">
@@ -11883,7 +11883,7 @@
         <v>237</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.002229</v>
+        <v>-0.002235</v>
       </c>
     </row>
     <row r="883">
@@ -11909,7 +11909,7 @@
         <v>239</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.001743</v>
+        <v>-0.001746</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>240</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.001674</v>
+        <v>-0.001673</v>
       </c>
     </row>
     <row r="886">
@@ -11961,7 +11961,7 @@
         <v>243</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.001387</v>
+        <v>-0.00139</v>
       </c>
     </row>
     <row r="889">
@@ -12104,7 +12104,7 @@
         <v>254</v>
       </c>
       <c r="C899" t="n">
-        <v>0.001861</v>
+        <v>0.001862</v>
       </c>
     </row>
     <row r="900">
@@ -12130,7 +12130,7 @@
         <v>256</v>
       </c>
       <c r="C901" t="n">
-        <v>0.00224</v>
+        <v>0.002241</v>
       </c>
     </row>
     <row r="902">
@@ -12156,7 +12156,7 @@
         <v>258</v>
       </c>
       <c r="C903" t="n">
-        <v>0.002547</v>
+        <v>0.00255</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>259</v>
       </c>
       <c r="C904" t="n">
-        <v>0.00262</v>
+        <v>0.002621</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>260</v>
       </c>
       <c r="C905" t="n">
-        <v>0.002726</v>
+        <v>0.002725</v>
       </c>
     </row>
     <row r="906">
@@ -12208,7 +12208,7 @@
         <v>262</v>
       </c>
       <c r="C907" t="n">
-        <v>0.003223</v>
+        <v>0.003224</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>263</v>
       </c>
       <c r="C908" t="n">
-        <v>0.003379</v>
+        <v>0.003381</v>
       </c>
     </row>
     <row r="909">
@@ -12247,7 +12247,7 @@
         <v>265</v>
       </c>
       <c r="C910" t="n">
-        <v>0.003932</v>
+        <v>0.003935</v>
       </c>
     </row>
     <row r="911">
@@ -12364,7 +12364,7 @@
         <v>274</v>
       </c>
       <c r="C919" t="n">
-        <v>0.005664</v>
+        <v>0.005672</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>275</v>
       </c>
       <c r="C920" t="n">
-        <v>0.005687</v>
+        <v>0.00569</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>276</v>
       </c>
       <c r="C921" t="n">
-        <v>0.005835</v>
+        <v>0.005837</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>277</v>
       </c>
       <c r="C922" t="n">
-        <v>0.006023</v>
+        <v>0.006025</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>278</v>
       </c>
       <c r="C923" t="n">
-        <v>0.006073</v>
+        <v>0.006083</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>279</v>
       </c>
       <c r="C924" t="n">
-        <v>0.006608</v>
+        <v>0.00661</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>280</v>
       </c>
       <c r="C925" t="n">
-        <v>0.006897</v>
+        <v>0.006898</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>281</v>
       </c>
       <c r="C926" t="n">
-        <v>0.007442</v>
+        <v>0.007443</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>282</v>
       </c>
       <c r="C927" t="n">
-        <v>0.008368</v>
+        <v>0.008369</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>283</v>
       </c>
       <c r="C928" t="n">
-        <v>0.008512</v>
+        <v>0.008510999999999999</v>
       </c>
     </row>
     <row r="929">
@@ -12507,7 +12507,7 @@
         <v>285</v>
       </c>
       <c r="C930" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008879</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>286</v>
       </c>
       <c r="C931" t="n">
-        <v>0.008985</v>
+        <v>0.008987</v>
       </c>
     </row>
     <row r="932">
@@ -12546,7 +12546,7 @@
         <v>288</v>
       </c>
       <c r="C933" t="n">
-        <v>0.009202</v>
+        <v>0.009202999999999999</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>289</v>
       </c>
       <c r="C934" t="n">
-        <v>0.009339999999999999</v>
+        <v>0.009351999999999999</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>290</v>
       </c>
       <c r="C935" t="n">
-        <v>0.009495999999999999</v>
+        <v>0.009497</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>291</v>
       </c>
       <c r="C936" t="n">
-        <v>0.009577</v>
+        <v>0.009575999999999999</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>292</v>
       </c>
       <c r="C937" t="n">
-        <v>0.009887</v>
+        <v>0.009894</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>293</v>
       </c>
       <c r="C938" t="n">
-        <v>0.010131</v>
+        <v>0.010144</v>
       </c>
     </row>
     <row r="939">
@@ -12637,7 +12637,7 @@
         <v>295</v>
       </c>
       <c r="C940" t="n">
-        <v>0.010962</v>
+        <v>0.010969</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>296</v>
       </c>
       <c r="C941" t="n">
-        <v>0.010971</v>
+        <v>0.010975</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>297</v>
       </c>
       <c r="C942" t="n">
-        <v>0.011055</v>
+        <v>0.011054</v>
       </c>
     </row>
     <row r="943">
@@ -12689,7 +12689,7 @@
         <v>299</v>
       </c>
       <c r="C944" t="n">
-        <v>0.011298</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>300</v>
       </c>
       <c r="C945" t="n">
-        <v>0.011497</v>
+        <v>0.011512</v>
       </c>
     </row>
     <row r="946">
@@ -12728,7 +12728,7 @@
         <v>302</v>
       </c>
       <c r="C947" t="n">
-        <v>0.011618</v>
+        <v>0.011617</v>
       </c>
     </row>
     <row r="948">
@@ -12754,7 +12754,7 @@
         <v>304</v>
       </c>
       <c r="C949" t="n">
-        <v>0.012366</v>
+        <v>0.012368</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>305</v>
       </c>
       <c r="C950" t="n">
-        <v>0.012375</v>
+        <v>0.012374</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>306</v>
       </c>
       <c r="C951" t="n">
-        <v>0.01257</v>
+        <v>0.012571</v>
       </c>
     </row>
     <row r="952">
@@ -12819,7 +12819,7 @@
         <v>309</v>
       </c>
       <c r="C954" t="n">
-        <v>0.013098</v>
+        <v>0.013099</v>
       </c>
     </row>
     <row r="955">
@@ -12845,7 +12845,7 @@
         <v>311</v>
       </c>
       <c r="C956" t="n">
-        <v>0.013673</v>
+        <v>0.013679</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>312</v>
       </c>
       <c r="C957" t="n">
-        <v>0.013806</v>
+        <v>0.01381</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>313</v>
       </c>
       <c r="C958" t="n">
-        <v>0.014188</v>
+        <v>0.014189</v>
       </c>
     </row>
     <row r="959">
@@ -12897,7 +12897,7 @@
         <v>315</v>
       </c>
       <c r="C960" t="n">
-        <v>0.014313</v>
+        <v>0.014312</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>316</v>
       </c>
       <c r="C961" t="n">
-        <v>0.014401</v>
+        <v>0.014405</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>317</v>
       </c>
       <c r="C962" t="n">
-        <v>0.014488</v>
+        <v>0.014493</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>318</v>
       </c>
       <c r="C963" t="n">
-        <v>0.014691</v>
+        <v>0.014699</v>
       </c>
     </row>
     <row r="964">
@@ -12962,7 +12962,7 @@
         <v>320</v>
       </c>
       <c r="C965" t="n">
-        <v>0.015061</v>
+        <v>0.01506</v>
       </c>
     </row>
     <row r="966">
@@ -12988,7 +12988,7 @@
         <v>322</v>
       </c>
       <c r="C967" t="n">
-        <v>0.015147</v>
+        <v>0.015172</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>323</v>
       </c>
       <c r="C968" t="n">
-        <v>0.015566</v>
+        <v>0.015565</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>324</v>
       </c>
       <c r="C969" t="n">
-        <v>0.015682</v>
+        <v>0.015681</v>
       </c>
     </row>
     <row r="970">
@@ -13040,7 +13040,7 @@
         <v>326</v>
       </c>
       <c r="C971" t="n">
-        <v>0.016552</v>
+        <v>0.01655</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>327</v>
       </c>
       <c r="C972" t="n">
-        <v>0.01673</v>
+        <v>0.016729</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>328</v>
       </c>
       <c r="C973" t="n">
-        <v>0.016756</v>
+        <v>0.016762</v>
       </c>
     </row>
     <row r="974">
@@ -13092,7 +13092,7 @@
         <v>330</v>
       </c>
       <c r="C975" t="n">
-        <v>0.017248</v>
+        <v>0.017247</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>331</v>
       </c>
       <c r="C976" t="n">
-        <v>0.017282</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>332</v>
       </c>
       <c r="C977" t="n">
-        <v>0.017705</v>
+        <v>0.017706</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>333</v>
       </c>
       <c r="C978" t="n">
-        <v>0.017771</v>
+        <v>0.017772</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>334</v>
       </c>
       <c r="C979" t="n">
-        <v>0.017881</v>
+        <v>0.01789</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>335</v>
       </c>
       <c r="C980" t="n">
-        <v>0.018148</v>
+        <v>0.018157</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>336</v>
       </c>
       <c r="C981" t="n">
-        <v>0.018559</v>
+        <v>0.018557</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>337</v>
       </c>
       <c r="C982" t="n">
-        <v>0.018854</v>
+        <v>0.018858</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>338</v>
       </c>
       <c r="C983" t="n">
-        <v>0.019102</v>
+        <v>0.019108</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>339</v>
       </c>
       <c r="C984" t="n">
-        <v>0.019402</v>
+        <v>0.01941</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>340</v>
       </c>
       <c r="C985" t="n">
-        <v>0.019437</v>
+        <v>0.019439</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>341</v>
       </c>
       <c r="C986" t="n">
-        <v>0.019447</v>
+        <v>0.019449</v>
       </c>
     </row>
     <row r="987">
@@ -13261,7 +13261,7 @@
         <v>343</v>
       </c>
       <c r="C988" t="n">
-        <v>0.019685</v>
+        <v>0.019683</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>344</v>
       </c>
       <c r="C989" t="n">
-        <v>0.01971</v>
+        <v>0.019713</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>345</v>
       </c>
       <c r="C990" t="n">
-        <v>0.020222</v>
+        <v>0.02024</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>346</v>
       </c>
       <c r="C991" t="n">
-        <v>0.020361</v>
+        <v>0.020369</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>347</v>
       </c>
       <c r="C992" t="n">
-        <v>0.021002</v>
+        <v>0.021003</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>348</v>
       </c>
       <c r="C993" t="n">
-        <v>0.021064</v>
+        <v>0.021062</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>349</v>
       </c>
       <c r="C994" t="n">
-        <v>0.021474</v>
+        <v>0.021476</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>350</v>
       </c>
       <c r="C995" t="n">
-        <v>0.021496</v>
+        <v>0.021495</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>351</v>
       </c>
       <c r="C996" t="n">
-        <v>0.021845</v>
+        <v>0.021843</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>352</v>
       </c>
       <c r="C997" t="n">
-        <v>0.021976</v>
+        <v>0.021974</v>
       </c>
     </row>
     <row r="998">
@@ -13391,7 +13391,7 @@
         <v>353</v>
       </c>
       <c r="C998" t="n">
-        <v>0.022788</v>
+        <v>0.022792</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>354</v>
       </c>
       <c r="C999" t="n">
-        <v>0.023098</v>
+        <v>0.023111</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>355</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.023157</v>
+        <v>0.023155</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>356</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.023223</v>
+        <v>0.023273</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>357</v>
       </c>
       <c r="C1002" t="n">
-        <v>0.023515</v>
+        <v>0.023514</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>358</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.023789</v>
+        <v>0.023793</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>359</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.023898</v>
+        <v>0.023897</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>360</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.023916</v>
+        <v>0.023914</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>361</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.024293</v>
+        <v>0.024291</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>362</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.024473</v>
+        <v>0.024482</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>363</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.024644</v>
+        <v>0.024642</v>
       </c>
     </row>
     <row r="1009">
@@ -13547,7 +13547,7 @@
         <v>365</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.024863</v>
+        <v>0.024862</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>366</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.025064</v>
+        <v>0.025063</v>
       </c>
     </row>
     <row r="1012">
@@ -13586,7 +13586,7 @@
         <v>368</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.025862</v>
+        <v>0.025863</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>369</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.025941</v>
+        <v>0.025949</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>370</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.026052</v>
+        <v>0.026053</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>371</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.026138</v>
+        <v>0.026148</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>372</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.02636</v>
+        <v>0.026358</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>373</v>
       </c>
       <c r="C1018" t="n">
-        <v>0.026446</v>
+        <v>0.026444</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>374</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.026516</v>
+        <v>0.026517</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>375</v>
       </c>
       <c r="C1020" t="n">
-        <v>0.026641</v>
+        <v>0.026639</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>376</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.02682</v>
+        <v>0.026818</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>377</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.027059</v>
+        <v>0.027076</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>378</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.02864</v>
+        <v>0.028642</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>379</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.028712</v>
+        <v>0.02872</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>380</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.028964</v>
+        <v>0.028981</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>381</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.029085</v>
+        <v>0.029082</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>382</v>
       </c>
       <c r="C1027" t="n">
-        <v>0.029103</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>383</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.029154</v>
+        <v>0.029155</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>384</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.029248</v>
+        <v>0.029259</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>385</v>
       </c>
       <c r="C1030" t="n">
-        <v>0.029646</v>
+        <v>0.029645</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>386</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.029904</v>
+        <v>0.029914</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>387</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.029975</v>
+        <v>0.029973</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>388</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.030369</v>
+        <v>0.030387</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>389</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.030567</v>
+        <v>0.030572</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>390</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.030755</v>
+        <v>0.030764</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>391</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.031062</v>
+        <v>0.031061</v>
       </c>
     </row>
     <row r="1037">
@@ -13911,7 +13911,7 @@
         <v>393</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.0313</v>
+        <v>0.031301</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>394</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.031647</v>
+        <v>0.031649</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>395</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.03198</v>
+        <v>0.031982</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>396</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.032136</v>
+        <v>0.032186</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>397</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.032478</v>
+        <v>0.032477</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>398</v>
       </c>
       <c r="C1043" t="n">
-        <v>0.032531</v>
+        <v>0.032528</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>399</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.032606</v>
+        <v>0.032604</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>400</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.033063</v>
+        <v>0.033092</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>401</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.033255</v>
+        <v>0.033253</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>402</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.033259</v>
+        <v>0.033267</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>403</v>
       </c>
       <c r="C1048" t="n">
-        <v>0.033562</v>
+        <v>0.033559</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>404</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.033796</v>
+        <v>0.033812</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>405</v>
       </c>
       <c r="C1050" t="n">
-        <v>0.03383</v>
+        <v>0.033828</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>406</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.033869</v>
+        <v>0.033889</v>
       </c>
     </row>
     <row r="1052">
@@ -14106,7 +14106,7 @@
         <v>408</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.034048</v>
+        <v>0.034046</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>409</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.034462</v>
+        <v>0.034472</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>410</v>
       </c>
       <c r="C1055" t="n">
-        <v>0.035106</v>
+        <v>0.035103</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>411</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.035169</v>
+        <v>0.035171</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>412</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.035599</v>
+        <v>0.035605</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>413</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.035861</v>
+        <v>0.035883</v>
       </c>
     </row>
     <row r="1059">
@@ -14197,7 +14197,7 @@
         <v>415</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.036095</v>
+        <v>0.036099</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>416</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.036176</v>
+        <v>0.036201</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>417</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.036472</v>
+        <v>0.036503</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>418</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.036644</v>
+        <v>0.036642</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>419</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.037008</v>
+        <v>0.037025</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>420</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.037136</v>
+        <v>0.037161</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>421</v>
       </c>
       <c r="C1066" t="n">
-        <v>0.037214</v>
+        <v>0.037211</v>
       </c>
     </row>
     <row r="1067">
@@ -14301,7 +14301,7 @@
         <v>423</v>
       </c>
       <c r="C1068" t="n">
-        <v>0.038142</v>
+        <v>0.03814</v>
       </c>
     </row>
     <row r="1069">
@@ -14327,7 +14327,7 @@
         <v>425</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.038724</v>
+        <v>0.038731</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>426</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.038919</v>
+        <v>0.038918</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>427</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.039522</v>
+        <v>0.03952</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>428</v>
       </c>
       <c r="C1073" t="n">
-        <v>0.039789</v>
+        <v>0.039786</v>
       </c>
     </row>
     <row r="1074">
@@ -14392,7 +14392,7 @@
         <v>430</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.040018</v>
+        <v>0.040017</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>431</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.040044</v>
+        <v>0.040065</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>432</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.040321</v>
+        <v>0.040335</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>433</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.040743</v>
+        <v>0.04074</v>
       </c>
     </row>
     <row r="1079">
@@ -14457,7 +14457,7 @@
         <v>435</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.041123</v>
+        <v>0.04113</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>436</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.041185</v>
+        <v>0.041199</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>437</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.04125</v>
+        <v>0.041262</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>438</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.042813</v>
+        <v>0.042811</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>439</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.042952</v>
+        <v>0.042974</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>440</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.043174</v>
+        <v>0.043175</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>441</v>
       </c>
       <c r="C1086" t="n">
-        <v>0.043264</v>
+        <v>0.04326</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>442</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.043613</v>
+        <v>0.043612</v>
       </c>
     </row>
     <row r="1088">
@@ -14574,7 +14574,7 @@
         <v>444</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.043885</v>
+        <v>0.043887</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>445</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.044298</v>
+        <v>0.04432</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>446</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.044318</v>
+        <v>0.044321</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>447</v>
       </c>
       <c r="C1092" t="n">
-        <v>0.044629</v>
+        <v>0.044625</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>448</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.044724</v>
+        <v>0.044727</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>449</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.044916</v>
+        <v>0.044938</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>450</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.044917</v>
+        <v>0.045102</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>451</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.045073</v>
+        <v>0.045316</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>452</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.045296</v>
+        <v>0.04549</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>453</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.045467</v>
+        <v>0.045521</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>454</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.045516</v>
+        <v>0.04569</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>455</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.045657</v>
+        <v>0.04579</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>456</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.045787</v>
+        <v>0.045881</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>457</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.045865</v>
+        <v>0.046337</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>458</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.046332</v>
+        <v>0.046881</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>459</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.046879</v>
+        <v>0.047095</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>460</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.047047</v>
+        <v>0.047313</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>461</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.047301</v>
+        <v>0.047476</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>462</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.047434</v>
+        <v>0.047669</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>463</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.04767</v>
+        <v>0.047815</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>464</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.047805</v>
+        <v>0.048763</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>465</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.04876</v>
+        <v>0.049183</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>466</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.049165</v>
+        <v>0.049206</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>467</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.049207</v>
+        <v>0.049976</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>468</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.049972</v>
+        <v>0.050003</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>469</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.050003</v>
+        <v>0.050261</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>470</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.050263</v>
+        <v>0.050632</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>471</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.050604</v>
+        <v>0.050917</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>472</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.050917</v>
+        <v>0.051251</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>473</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.051233</v>
+        <v>0.051402</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>474</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.051402</v>
+        <v>0.052688</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>475</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.052692</v>
+        <v>0.052792</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>476</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.052796</v>
+        <v>0.052956</v>
       </c>
     </row>
     <row r="1122">
@@ -15003,7 +15003,7 @@
         <v>477</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.052958</v>
+        <v>0.053137</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>478</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.053098</v>
+        <v>0.05317</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>479</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.05317</v>
+        <v>0.053906</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>480</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.053901</v>
+        <v>0.054032</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>481</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.054036</v>
+        <v>0.054064</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>482</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.054064</v>
+        <v>0.054413</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>483</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.054416</v>
+        <v>0.054448</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>484</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.054452</v>
+        <v>0.054613</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>485</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.054614</v>
+        <v>0.054743</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>486</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.054727</v>
+        <v>0.054783</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>487</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.054759</v>
+        <v>0.054821</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>488</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.05482</v>
+        <v>0.055472</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>489</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.055456</v>
+        <v>0.055699</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>490</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.055688</v>
+        <v>0.055733</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>491</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.055737</v>
+        <v>0.056256</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>492</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.056254</v>
+        <v>0.056484</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>493</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.056486</v>
+        <v>0.057176</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>494</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.057153</v>
+        <v>0.057438</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>495</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.057442</v>
+        <v>0.057493</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>496</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.057477</v>
+        <v>0.057531</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>497</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.057535</v>
+        <v>0.058073</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>498</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.05807</v>
+        <v>0.059132</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>499</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.059125</v>
+        <v>0.059805</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>500</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.059806</v>
+        <v>0.059826</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>501</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.059827</v>
+        <v>0.059987</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>502</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.059988</v>
+        <v>0.060222</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>503</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.060226</v>
+        <v>0.060689</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>504</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.060626</v>
+        <v>0.060844</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>505</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.06085</v>
+        <v>0.060851</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>506</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.061945</v>
+        <v>0.061943</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>507</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.062151</v>
+        <v>0.062156</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>508</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.06274200000000001</v>
+        <v>0.062738</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>509</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.06345199999999999</v>
+        <v>0.063453</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>510</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.06353200000000001</v>
+        <v>0.06353499999999999</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>511</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.06395099999999999</v>
+        <v>0.063947</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>512</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.064552</v>
+        <v>0.06455</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>513</v>
       </c>
       <c r="C1158" t="n">
-        <v>0.065026</v>
+        <v>0.065022</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>514</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.065577</v>
+        <v>0.06557399999999999</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>515</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.065888</v>
+        <v>0.065883</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>516</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.066051</v>
+        <v>0.066048</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>517</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.06736200000000001</v>
+        <v>0.06736399999999999</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>518</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.068051</v>
+        <v>0.068092</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>519</v>
       </c>
       <c r="C1164" t="n">
-        <v>0.068313</v>
+        <v>0.06830899999999999</v>
       </c>
     </row>
     <row r="1165">
@@ -15575,7 +15575,7 @@
         <v>521</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.068908</v>
+        <v>0.068915</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>522</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.06926599999999999</v>
+        <v>0.069267</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>523</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.069298</v>
+        <v>0.069316</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>524</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.069538</v>
+        <v>0.06954100000000001</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>525</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.070239</v>
+        <v>0.070257</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>526</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.07033</v>
+        <v>0.070325</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>527</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.07091600000000001</v>
+        <v>0.070911</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>528</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.07098</v>
+        <v>0.071007</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>529</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.071259</v>
+        <v>0.071254</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>530</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.072227</v>
+        <v>0.07222099999999999</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>531</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.07230399999999999</v>
+        <v>0.0723</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>532</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.072839</v>
+        <v>0.072843</v>
       </c>
     </row>
     <row r="1178">
@@ -15744,7 +15744,7 @@
         <v>534</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.07391200000000001</v>
+        <v>0.073911</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>535</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.074473</v>
+        <v>0.074502</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>536</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.07470400000000001</v>
+        <v>0.07470599999999999</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>537</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.074916</v>
+        <v>0.074924</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>538</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.075199</v>
+        <v>0.075193</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>539</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.075471</v>
+        <v>0.07547</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>540</v>
       </c>
       <c r="C1185" t="n">
-        <v>0.075558</v>
+        <v>0.075553</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>541</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.076393</v>
+        <v>0.076388</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>542</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.078482</v>
+        <v>0.078573</v>
       </c>
     </row>
     <row r="1188">
@@ -15874,7 +15874,7 @@
         <v>544</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.078916</v>
+        <v>0.07892299999999999</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>545</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.079387</v>
+        <v>0.079388</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>546</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.079745</v>
+        <v>0.07974199999999999</v>
       </c>
     </row>
     <row r="1192">
@@ -15926,7 +15926,7 @@
         <v>548</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.080814</v>
+        <v>0.08083600000000001</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>549</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.08167199999999999</v>
+        <v>0.081735</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>550</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.08194700000000001</v>
+        <v>0.081951</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>551</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.082467</v>
+        <v>0.082499</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>552</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.083384</v>
+        <v>0.08337799999999999</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>553</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.08358400000000001</v>
+        <v>0.083583</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>554</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.08388</v>
+        <v>0.083938</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>555</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.084398</v>
+        <v>0.084576</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>556</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.08472</v>
+        <v>0.084719</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>557</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.084755</v>
+        <v>0.08475100000000001</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>558</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.08584799999999999</v>
+        <v>0.085843</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>559</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.08654100000000001</v>
+        <v>0.086544</v>
       </c>
     </row>
     <row r="1205">
@@ -16095,7 +16095,7 @@
         <v>561</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.088405</v>
+        <v>0.088437</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>562</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.08878</v>
+        <v>0.08877699999999999</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>563</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.088813</v>
+        <v>0.088814</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>564</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.091626</v>
+        <v>0.09166000000000001</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>565</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.09197</v>
+        <v>0.091963</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>566</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.092641</v>
+        <v>0.092638</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>567</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.092949</v>
+        <v>0.092974</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>568</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.09314699999999999</v>
+        <v>0.09322800000000001</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>569</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.095321</v>
+        <v>0.09531299999999999</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>570</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.095959</v>
+        <v>0.095986</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>571</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.096373</v>
+        <v>0.09646299999999999</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>572</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.096426</v>
+        <v>0.096598</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>573</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.096605</v>
+        <v>0.09664300000000001</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>574</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.097092</v>
+        <v>0.09711500000000001</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>575</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.09751899999999999</v>
+        <v>0.097513</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>576</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.09888</v>
+        <v>0.09893299999999999</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>577</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.100086</v>
+        <v>0.100096</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>578</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.1002</v>
+        <v>0.100195</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>579</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.100554</v>
+        <v>0.100556</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>580</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.100806</v>
+        <v>0.10095</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>581</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.101023</v>
+        <v>0.101015</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>582</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.102149</v>
+        <v>0.102143</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>583</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.102622</v>
+        <v>0.102633</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>584</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.104264</v>
+        <v>0.104279</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>585</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.109143</v>
+        <v>0.10914</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>586</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.109404</v>
+        <v>0.109401</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>587</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.109762</v>
+        <v>0.109768</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>588</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.109952</v>
+        <v>0.10997</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>589</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.110237</v>
+        <v>0.11023</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>590</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.110819</v>
+        <v>0.11088</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>591</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.114393</v>
+        <v>0.114411</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>592</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.11559</v>
+        <v>0.115581</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>593</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.117709</v>
+        <v>0.117714</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>594</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.119532</v>
+        <v>0.119529</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>595</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.120373</v>
+        <v>0.120364</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>596</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.121819</v>
+        <v>0.121831</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>597</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.12322</v>
+        <v>0.123212</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>598</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.124747</v>
+        <v>0.124877</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>599</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.125198</v>
+        <v>0.125206</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>600</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.125839</v>
+        <v>0.125832</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>601</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.126142</v>
+        <v>0.126143</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>602</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.130816</v>
+        <v>0.130809</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>603</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.131529</v>
+        <v>0.131534</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>604</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.133028</v>
+        <v>0.133027</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>605</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.136036</v>
+        <v>0.136031</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>606</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.136375</v>
+        <v>0.136377</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>607</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.136663</v>
+        <v>0.136657</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>608</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.13729</v>
+        <v>0.137347</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>609</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.140549</v>
+        <v>0.140633</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>610</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.141191</v>
+        <v>0.14119</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>611</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.142093</v>
+        <v>0.142085</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>612</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.142878</v>
+        <v>0.14288</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>613</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.14393</v>
+        <v>0.143946</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>614</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.146313</v>
+        <v>0.146383</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>615</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.153331</v>
+        <v>0.153326</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>616</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.155832</v>
+        <v>0.155822</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>617</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.159144</v>
+        <v>0.159132</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>618</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.161132</v>
+        <v>0.161128</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>619</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.161282</v>
+        <v>0.161328</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>620</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.171001</v>
+        <v>0.171011</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>621</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.176689</v>
+        <v>0.176735</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>622</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.18016</v>
+        <v>0.180146</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>623</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.18214</v>
+        <v>0.182164</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>624</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.18322</v>
+        <v>0.183245</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>625</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.183821</v>
+        <v>0.184192</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>626</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.187537</v>
+        <v>0.187522</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>627</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.187818</v>
+        <v>0.1879</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>628</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.188479</v>
+        <v>0.188467</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>629</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.189068</v>
+        <v>0.189223</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>630</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.198512</v>
+        <v>0.198508</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>631</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.199406</v>
+        <v>0.199544</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>632</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.207827</v>
+        <v>0.207823</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>633</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.247202</v>
+        <v>0.247184</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>634</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.247202</v>
+        <v>0.247336</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>635</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.263604</v>
+        <v>0.263887</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>636</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>637</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.270696</v>
+        <v>0.271167</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>638</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.27628</v>
+        <v>0.27639</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>639</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>640</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.349304</v>
+        <v>0.349364</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>641</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.362633</v>
+        <v>0.362846</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>642</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.507092</v>
+        <v>0.507274</v>
       </c>
     </row>
   </sheetData>
